--- a/artfynd/A 44372-2024 artfynd.xlsx
+++ b/artfynd/A 44372-2024 artfynd.xlsx
@@ -1021,10 +1021,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120325729</v>
+        <v>120325831</v>
       </c>
       <c r="B5" t="n">
-        <v>57320</v>
+        <v>78542</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1037,42 +1037,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Getklövbäcken, Getklövbäcken, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>578537</v>
+        <v>578573</v>
       </c>
       <c r="R5" t="n">
-        <v>7053266</v>
+        <v>7053238</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1104,7 +1096,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1114,7 +1106,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1141,10 +1133,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120325831</v>
+        <v>120325801</v>
       </c>
       <c r="B6" t="n">
-        <v>78542</v>
+        <v>57320</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1157,34 +1149,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Getklövbäcken, Getklövbäcken, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>578573</v>
+        <v>578563</v>
       </c>
       <c r="R6" t="n">
-        <v>7053238</v>
+        <v>7053248</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1216,7 +1213,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1226,7 +1223,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:02</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1241,19 +1243,19 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120325801</v>
+        <v>120325729</v>
       </c>
       <c r="B7" t="n">
         <v>57320</v>
@@ -1287,21 +1289,24 @@
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
           <t>färska spår</t>
         </is>
       </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Getklövbäcken, Getklövbäcken, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>578563</v>
+        <v>578537</v>
       </c>
       <c r="R7" t="n">
-        <v>7053248</v>
+        <v>7053266</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1333,7 +1338,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1343,12 +1348,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>16:02</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1363,12 +1363,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -1492,10 +1492,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120326941</v>
+        <v>120324440</v>
       </c>
       <c r="B9" t="n">
-        <v>57320</v>
+        <v>78542</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1508,39 +1508,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Getklövbäcken, Getklövbäcken, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>578608</v>
+        <v>578366</v>
       </c>
       <c r="R9" t="n">
-        <v>7053279</v>
+        <v>7053383</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1572,7 +1567,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1582,12 +1577,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>16:36</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1602,22 +1592,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120324440</v>
+        <v>120326941</v>
       </c>
       <c r="B10" t="n">
-        <v>78542</v>
+        <v>57320</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1630,34 +1620,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Getklövbäcken, Getklövbäcken, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>578366</v>
+        <v>578608</v>
       </c>
       <c r="R10" t="n">
-        <v>7053383</v>
+        <v>7053279</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1689,7 +1684,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1699,7 +1694,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>16:36</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1714,12 +1714,12 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>

--- a/artfynd/A 44372-2024 artfynd.xlsx
+++ b/artfynd/A 44372-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120325878</v>
+        <v>120326566</v>
       </c>
       <c r="B2" t="n">
-        <v>57320</v>
+        <v>90864</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,39 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Getklövbäcken, Getklövbäcken, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>578640</v>
+        <v>578709</v>
       </c>
       <c r="R2" t="n">
-        <v>7053180</v>
+        <v>7053176</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>16:34</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,12 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>16:08</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>16:34</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -785,19 +775,19 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120326636</v>
+        <v>120323632</v>
       </c>
       <c r="B3" t="n">
         <v>78542</v>
@@ -837,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>578697</v>
+        <v>578327</v>
       </c>
       <c r="R3" t="n">
-        <v>7053183</v>
+        <v>7053358</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -872,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -882,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -909,7 +899,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120323632</v>
+        <v>120326636</v>
       </c>
       <c r="B4" t="n">
         <v>78542</v>
@@ -949,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>578327</v>
+        <v>578697</v>
       </c>
       <c r="R4" t="n">
-        <v>7053358</v>
+        <v>7053183</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -984,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -994,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1021,7 +1011,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120325831</v>
+        <v>120326804</v>
       </c>
       <c r="B5" t="n">
         <v>78542</v>
@@ -1061,10 +1051,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>578573</v>
+        <v>578652</v>
       </c>
       <c r="R5" t="n">
-        <v>7053238</v>
+        <v>7053230</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1096,7 +1086,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1106,7 +1096,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1133,7 +1123,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120325801</v>
+        <v>120325729</v>
       </c>
       <c r="B6" t="n">
         <v>57320</v>
@@ -1167,21 +1157,24 @@
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
           <t>färska spår</t>
         </is>
       </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Getklövbäcken, Getklövbäcken, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>578563</v>
+        <v>578537</v>
       </c>
       <c r="R6" t="n">
-        <v>7053248</v>
+        <v>7053266</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1213,7 +1206,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1223,12 +1216,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>16:02</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1243,22 +1231,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120325729</v>
+        <v>120325831</v>
       </c>
       <c r="B7" t="n">
-        <v>57320</v>
+        <v>78542</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1271,42 +1259,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Getklövbäcken, Getklövbäcken, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>578537</v>
+        <v>578573</v>
       </c>
       <c r="R7" t="n">
-        <v>7053266</v>
+        <v>7053238</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1338,7 +1318,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1348,7 +1328,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1375,10 +1355,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120325418</v>
+        <v>120324440</v>
       </c>
       <c r="B8" t="n">
-        <v>57320</v>
+        <v>78542</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1391,39 +1371,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Getklövbäcken, Getklövbäcken, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>578482</v>
+        <v>578366</v>
       </c>
       <c r="R8" t="n">
-        <v>7053311</v>
+        <v>7053383</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1455,7 +1430,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1465,7 +1440,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1480,22 +1455,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120324440</v>
+        <v>120325878</v>
       </c>
       <c r="B9" t="n">
-        <v>78542</v>
+        <v>57320</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1508,34 +1483,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Getklövbäcken, Getklövbäcken, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>578366</v>
+        <v>578640</v>
       </c>
       <c r="R9" t="n">
-        <v>7053383</v>
+        <v>7053180</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1567,7 +1547,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1577,7 +1557,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>16:08</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1592,22 +1577,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120326941</v>
+        <v>120326814</v>
       </c>
       <c r="B10" t="n">
-        <v>57320</v>
+        <v>95225</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1616,33 +1601,28 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>2869</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Getklövbäcken, Getklövbäcken, Ång</t>
@@ -1684,7 +1664,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1694,12 +1674,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>16:36</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1726,10 +1701,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120326814</v>
+        <v>120325624</v>
       </c>
       <c r="B11" t="n">
-        <v>95225</v>
+        <v>78542</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1738,25 +1713,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2869</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1766,10 +1741,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>578608</v>
+        <v>578481</v>
       </c>
       <c r="R11" t="n">
-        <v>7053279</v>
+        <v>7053309</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1801,7 +1776,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1811,7 +1786,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1826,22 +1801,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120325624</v>
+        <v>120326941</v>
       </c>
       <c r="B12" t="n">
-        <v>78542</v>
+        <v>57320</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1854,34 +1829,39 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Getklövbäcken, Getklövbäcken, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>578481</v>
+        <v>578608</v>
       </c>
       <c r="R12" t="n">
-        <v>7053309</v>
+        <v>7053279</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1913,7 +1893,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1923,7 +1903,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>16:36</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1938,22 +1923,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120323572</v>
+        <v>120325801</v>
       </c>
       <c r="B13" t="n">
-        <v>78542</v>
+        <v>57320</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1966,34 +1951,39 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Getklövbäcken, Getklövbäcken, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>578342</v>
+        <v>578563</v>
       </c>
       <c r="R13" t="n">
-        <v>7053371</v>
+        <v>7053248</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2025,7 +2015,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2035,7 +2025,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>16:02</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2050,12 +2045,12 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
@@ -2174,10 +2169,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120326566</v>
+        <v>120325418</v>
       </c>
       <c r="B15" t="n">
-        <v>90864</v>
+        <v>57320</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2190,34 +2185,39 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Getklövbäcken, Getklövbäcken, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>578709</v>
+        <v>578482</v>
       </c>
       <c r="R15" t="n">
-        <v>7053176</v>
+        <v>7053311</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2249,7 +2249,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>16:34</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2259,7 +2259,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>16:34</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2274,12 +2274,12 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
@@ -2515,7 +2515,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120326804</v>
+        <v>120323572</v>
       </c>
       <c r="B18" t="n">
         <v>78542</v>
@@ -2555,10 +2555,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>578652</v>
+        <v>578342</v>
       </c>
       <c r="R18" t="n">
-        <v>7053230</v>
+        <v>7053371</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2590,7 +2590,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2600,7 +2600,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AD18" t="b">

--- a/artfynd/A 44372-2024 artfynd.xlsx
+++ b/artfynd/A 44372-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120326566</v>
+        <v>120324440</v>
       </c>
       <c r="B2" t="n">
-        <v>90864</v>
+        <v>78542</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>578709</v>
+        <v>578366</v>
       </c>
       <c r="R2" t="n">
-        <v>7053176</v>
+        <v>7053383</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>16:34</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>16:34</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120323632</v>
+        <v>120325729</v>
       </c>
       <c r="B3" t="n">
-        <v>78542</v>
+        <v>57320</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,34 +803,42 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Getklövbäcken, Getklövbäcken, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>578327</v>
+        <v>578537</v>
       </c>
       <c r="R3" t="n">
-        <v>7053358</v>
+        <v>7053266</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +870,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +880,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +907,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120326636</v>
+        <v>120326566</v>
       </c>
       <c r="B4" t="n">
-        <v>78542</v>
+        <v>90864</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,21 +923,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +947,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>578697</v>
+        <v>578709</v>
       </c>
       <c r="R4" t="n">
-        <v>7053183</v>
+        <v>7053176</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -974,7 +982,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>16:34</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +992,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>16:34</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,10 +1019,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120326804</v>
+        <v>120325418</v>
       </c>
       <c r="B5" t="n">
-        <v>78542</v>
+        <v>57320</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1027,34 +1035,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Getklövbäcken, Getklövbäcken, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>578652</v>
+        <v>578482</v>
       </c>
       <c r="R5" t="n">
-        <v>7053230</v>
+        <v>7053311</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1086,7 +1099,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1096,7 +1109,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1111,22 +1124,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120325729</v>
+        <v>120326814</v>
       </c>
       <c r="B6" t="n">
-        <v>57320</v>
+        <v>95225</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1135,46 +1148,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>2869</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Getklövbäcken, Getklövbäcken, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>578537</v>
+        <v>578608</v>
       </c>
       <c r="R6" t="n">
-        <v>7053266</v>
+        <v>7053279</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1206,7 +1211,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1216,7 +1221,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1231,19 +1236,19 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120325831</v>
+        <v>120326636</v>
       </c>
       <c r="B7" t="n">
         <v>78542</v>
@@ -1283,10 +1288,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>578573</v>
+        <v>578697</v>
       </c>
       <c r="R7" t="n">
-        <v>7053238</v>
+        <v>7053183</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1318,7 +1323,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1328,7 +1333,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1355,10 +1360,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120324440</v>
+        <v>120325878</v>
       </c>
       <c r="B8" t="n">
-        <v>78542</v>
+        <v>57320</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1371,34 +1376,39 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Getklövbäcken, Getklövbäcken, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>578366</v>
+        <v>578640</v>
       </c>
       <c r="R8" t="n">
-        <v>7053383</v>
+        <v>7053180</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1430,7 +1440,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1440,7 +1450,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>16:08</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1455,19 +1470,19 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120325878</v>
+        <v>120324175</v>
       </c>
       <c r="B9" t="n">
         <v>57320</v>
@@ -1501,21 +1516,16 @@
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Getklövbäcken, Getklövbäcken, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>578640</v>
+        <v>578371</v>
       </c>
       <c r="R9" t="n">
-        <v>7053180</v>
+        <v>7053353</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1547,7 +1557,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1557,12 +1567,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1577,22 +1587,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120326814</v>
+        <v>120325624</v>
       </c>
       <c r="B10" t="n">
-        <v>95225</v>
+        <v>78542</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1601,25 +1611,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2869</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1629,10 +1639,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>578608</v>
+        <v>578481</v>
       </c>
       <c r="R10" t="n">
-        <v>7053279</v>
+        <v>7053309</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1664,7 +1674,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1674,7 +1684,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1689,22 +1699,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120325624</v>
+        <v>120325801</v>
       </c>
       <c r="B11" t="n">
-        <v>78542</v>
+        <v>57320</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1717,34 +1727,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Getklövbäcken, Getklövbäcken, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>578481</v>
+        <v>578563</v>
       </c>
       <c r="R11" t="n">
-        <v>7053309</v>
+        <v>7053248</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1776,7 +1791,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1786,7 +1801,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>16:02</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1801,22 +1821,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120326941</v>
+        <v>120323572</v>
       </c>
       <c r="B12" t="n">
-        <v>57320</v>
+        <v>78542</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1829,39 +1849,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Getklövbäcken, Getklövbäcken, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>578608</v>
+        <v>578342</v>
       </c>
       <c r="R12" t="n">
-        <v>7053279</v>
+        <v>7053371</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1893,7 +1908,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1903,12 +1918,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>16:36</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1923,19 +1933,19 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120325801</v>
+        <v>120326941</v>
       </c>
       <c r="B13" t="n">
         <v>57320</v>
@@ -1980,10 +1990,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>578563</v>
+        <v>578608</v>
       </c>
       <c r="R13" t="n">
-        <v>7053248</v>
+        <v>7053279</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2015,7 +2025,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2025,7 +2035,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
@@ -2169,10 +2179,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120325418</v>
+        <v>120323551</v>
       </c>
       <c r="B15" t="n">
-        <v>57320</v>
+        <v>82321</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2185,39 +2195,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Getklövbäcken, Getklövbäcken, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>578482</v>
+        <v>578374</v>
       </c>
       <c r="R15" t="n">
-        <v>7053311</v>
+        <v>7053367</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2249,7 +2254,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2259,7 +2264,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2274,22 +2279,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120324175</v>
+        <v>120326804</v>
       </c>
       <c r="B16" t="n">
-        <v>57320</v>
+        <v>78542</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2302,21 +2307,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2326,10 +2331,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>578371</v>
+        <v>578652</v>
       </c>
       <c r="R16" t="n">
-        <v>7053353</v>
+        <v>7053230</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2361,7 +2366,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2371,12 +2376,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>15:37</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2403,10 +2403,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120323551</v>
+        <v>120323632</v>
       </c>
       <c r="B17" t="n">
-        <v>82321</v>
+        <v>78542</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2419,21 +2419,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2443,10 +2443,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>578374</v>
+        <v>578327</v>
       </c>
       <c r="R17" t="n">
-        <v>7053367</v>
+        <v>7053358</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2478,7 +2478,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2488,7 +2488,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2515,7 +2515,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120323572</v>
+        <v>120325831</v>
       </c>
       <c r="B18" t="n">
         <v>78542</v>
@@ -2555,10 +2555,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>578342</v>
+        <v>578573</v>
       </c>
       <c r="R18" t="n">
-        <v>7053371</v>
+        <v>7053238</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2590,7 +2590,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2600,7 +2600,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AD18" t="b">

--- a/artfynd/A 44372-2024 artfynd.xlsx
+++ b/artfynd/A 44372-2024 artfynd.xlsx
@@ -1019,10 +1019,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120325418</v>
+        <v>120326636</v>
       </c>
       <c r="B5" t="n">
-        <v>57320</v>
+        <v>78542</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1035,39 +1035,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Getklövbäcken, Getklövbäcken, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>578482</v>
+        <v>578697</v>
       </c>
       <c r="R5" t="n">
-        <v>7053311</v>
+        <v>7053183</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,7 +1094,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1109,7 +1104,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1124,12 +1119,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1248,10 +1243,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120326636</v>
+        <v>120325418</v>
       </c>
       <c r="B7" t="n">
-        <v>78542</v>
+        <v>57320</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1264,34 +1259,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Getklövbäcken, Getklövbäcken, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>578697</v>
+        <v>578482</v>
       </c>
       <c r="R7" t="n">
-        <v>7053183</v>
+        <v>7053311</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1323,7 +1323,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1333,7 +1333,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1348,12 +1348,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>

--- a/artfynd/A 44372-2024 artfynd.xlsx
+++ b/artfynd/A 44372-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120324440</v>
+        <v>120325878</v>
       </c>
       <c r="B2" t="n">
-        <v>78542</v>
+        <v>57320</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,39 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Getklövbäcken, Getklövbäcken, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>578366</v>
+        <v>578640</v>
       </c>
       <c r="R2" t="n">
-        <v>7053383</v>
+        <v>7053180</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +765,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>16:08</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,22 +785,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120325729</v>
+        <v>120326814</v>
       </c>
       <c r="B3" t="n">
-        <v>57320</v>
+        <v>95225</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,46 +809,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>2869</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Getklövbäcken, Getklövbäcken, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>578537</v>
+        <v>578608</v>
       </c>
       <c r="R3" t="n">
-        <v>7053266</v>
+        <v>7053279</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -870,7 +872,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -880,7 +882,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -895,22 +897,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120326566</v>
+        <v>120323551</v>
       </c>
       <c r="B4" t="n">
-        <v>90864</v>
+        <v>82321</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -923,21 +925,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>658</v>
+        <v>1312</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -947,10 +949,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>578709</v>
+        <v>578374</v>
       </c>
       <c r="R4" t="n">
-        <v>7053176</v>
+        <v>7053367</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -982,7 +984,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>16:34</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -992,7 +994,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>16:34</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1019,7 +1021,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120326636</v>
+        <v>120323572</v>
       </c>
       <c r="B5" t="n">
         <v>78542</v>
@@ -1059,10 +1061,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>578697</v>
+        <v>578342</v>
       </c>
       <c r="R5" t="n">
-        <v>7053183</v>
+        <v>7053371</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1094,7 +1096,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1104,7 +1106,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1131,10 +1133,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120326814</v>
+        <v>120324440</v>
       </c>
       <c r="B6" t="n">
-        <v>95225</v>
+        <v>78542</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1143,25 +1145,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2869</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1171,10 +1173,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>578608</v>
+        <v>578366</v>
       </c>
       <c r="R6" t="n">
-        <v>7053279</v>
+        <v>7053383</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1206,7 +1208,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1216,7 +1218,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1231,19 +1233,19 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120325418</v>
+        <v>120326941</v>
       </c>
       <c r="B7" t="n">
         <v>57320</v>
@@ -1288,10 +1290,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>578482</v>
+        <v>578608</v>
       </c>
       <c r="R7" t="n">
-        <v>7053311</v>
+        <v>7053279</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1323,7 +1325,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1333,7 +1335,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>16:36</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1360,7 +1367,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120325878</v>
+        <v>120325801</v>
       </c>
       <c r="B8" t="n">
         <v>57320</v>
@@ -1405,10 +1412,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>578640</v>
+        <v>578563</v>
       </c>
       <c r="R8" t="n">
-        <v>7053180</v>
+        <v>7053248</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1440,7 +1447,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1450,12 +1457,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1482,10 +1489,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120324175</v>
+        <v>120323632</v>
       </c>
       <c r="B9" t="n">
-        <v>57320</v>
+        <v>78542</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1498,21 +1505,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1522,10 +1529,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>578371</v>
+        <v>578327</v>
       </c>
       <c r="R9" t="n">
-        <v>7053353</v>
+        <v>7053358</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1557,7 +1564,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1567,12 +1574,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:37</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1599,7 +1601,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120325624</v>
+        <v>120323518</v>
       </c>
       <c r="B10" t="n">
         <v>78542</v>
@@ -1639,10 +1641,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>578481</v>
+        <v>578469</v>
       </c>
       <c r="R10" t="n">
-        <v>7053309</v>
+        <v>7053356</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1674,7 +1676,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1684,7 +1686,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1711,7 +1713,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120325801</v>
+        <v>120325729</v>
       </c>
       <c r="B11" t="n">
         <v>57320</v>
@@ -1745,21 +1747,24 @@
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
           <t>färska spår</t>
         </is>
       </c>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Getklövbäcken, Getklövbäcken, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>578563</v>
+        <v>578537</v>
       </c>
       <c r="R11" t="n">
-        <v>7053248</v>
+        <v>7053266</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1791,7 +1796,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1801,12 +1806,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>16:02</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1821,22 +1821,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120323572</v>
+        <v>120325418</v>
       </c>
       <c r="B12" t="n">
-        <v>78542</v>
+        <v>57320</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1849,34 +1849,39 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Getklövbäcken, Getklövbäcken, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>578342</v>
+        <v>578482</v>
       </c>
       <c r="R12" t="n">
-        <v>7053371</v>
+        <v>7053311</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1908,7 +1913,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1918,7 +1923,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1933,22 +1938,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120326941</v>
+        <v>120325624</v>
       </c>
       <c r="B13" t="n">
-        <v>57320</v>
+        <v>78542</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1961,39 +1966,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Getklövbäcken, Getklövbäcken, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>578608</v>
+        <v>578481</v>
       </c>
       <c r="R13" t="n">
-        <v>7053279</v>
+        <v>7053309</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2025,7 +2025,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2035,12 +2035,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>16:36</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2055,19 +2050,19 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120323518</v>
+        <v>120325831</v>
       </c>
       <c r="B14" t="n">
         <v>78542</v>
@@ -2107,10 +2102,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>578469</v>
+        <v>578573</v>
       </c>
       <c r="R14" t="n">
-        <v>7053356</v>
+        <v>7053238</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2142,7 +2137,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2152,7 +2147,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2179,10 +2174,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120323551</v>
+        <v>120326636</v>
       </c>
       <c r="B15" t="n">
-        <v>82321</v>
+        <v>78542</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2195,21 +2190,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2219,10 +2214,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>578374</v>
+        <v>578697</v>
       </c>
       <c r="R15" t="n">
-        <v>7053367</v>
+        <v>7053183</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2254,7 +2249,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2264,7 +2259,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2291,10 +2286,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120326804</v>
+        <v>120324175</v>
       </c>
       <c r="B16" t="n">
-        <v>78542</v>
+        <v>57320</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2307,21 +2302,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2331,10 +2326,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>578652</v>
+        <v>578371</v>
       </c>
       <c r="R16" t="n">
-        <v>7053230</v>
+        <v>7053353</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2366,7 +2361,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2376,7 +2371,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>15:37</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2403,10 +2403,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120323632</v>
+        <v>120326566</v>
       </c>
       <c r="B17" t="n">
-        <v>78542</v>
+        <v>90864</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2419,21 +2419,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2443,10 +2443,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>578327</v>
+        <v>578709</v>
       </c>
       <c r="R17" t="n">
-        <v>7053358</v>
+        <v>7053176</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2478,7 +2478,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:34</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2488,7 +2488,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:34</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2515,7 +2515,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120325831</v>
+        <v>120326804</v>
       </c>
       <c r="B18" t="n">
         <v>78542</v>
@@ -2555,10 +2555,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>578573</v>
+        <v>578652</v>
       </c>
       <c r="R18" t="n">
-        <v>7053238</v>
+        <v>7053230</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2590,7 +2590,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2600,7 +2600,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AD18" t="b">

--- a/artfynd/A 44372-2024 artfynd.xlsx
+++ b/artfynd/A 44372-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120325878</v>
+        <v>120323632</v>
       </c>
       <c r="B2" t="n">
-        <v>57320</v>
+        <v>78542</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,39 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Getklövbäcken, Getklövbäcken, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>578640</v>
+        <v>578327</v>
       </c>
       <c r="R2" t="n">
-        <v>7053180</v>
+        <v>7053358</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,12 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>16:08</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -785,22 +775,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120326814</v>
+        <v>120326804</v>
       </c>
       <c r="B3" t="n">
-        <v>95225</v>
+        <v>78542</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -809,25 +799,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2869</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -837,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>578608</v>
+        <v>578652</v>
       </c>
       <c r="R3" t="n">
-        <v>7053279</v>
+        <v>7053230</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -872,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -882,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -897,22 +887,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120323551</v>
+        <v>120323572</v>
       </c>
       <c r="B4" t="n">
-        <v>82321</v>
+        <v>78542</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -925,21 +915,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -949,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>578374</v>
+        <v>578342</v>
       </c>
       <c r="R4" t="n">
-        <v>7053367</v>
+        <v>7053371</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -984,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -994,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1021,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120323572</v>
+        <v>120325801</v>
       </c>
       <c r="B5" t="n">
-        <v>78542</v>
+        <v>57320</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1037,34 +1027,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Getklövbäcken, Getklövbäcken, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>578342</v>
+        <v>578563</v>
       </c>
       <c r="R5" t="n">
-        <v>7053371</v>
+        <v>7053248</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1096,7 +1091,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1106,7 +1101,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>16:02</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1121,22 +1121,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120324440</v>
+        <v>120325878</v>
       </c>
       <c r="B6" t="n">
-        <v>78542</v>
+        <v>57320</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1149,34 +1149,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Getklövbäcken, Getklövbäcken, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>578366</v>
+        <v>578640</v>
       </c>
       <c r="R6" t="n">
-        <v>7053383</v>
+        <v>7053180</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1208,7 +1213,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1218,7 +1223,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>16:08</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1233,22 +1243,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120326941</v>
+        <v>120326814</v>
       </c>
       <c r="B7" t="n">
-        <v>57320</v>
+        <v>95225</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1257,33 +1267,28 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>2869</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Getklövbäcken, Getklövbäcken, Ång</t>
@@ -1325,7 +1330,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1335,12 +1340,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>16:36</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1367,10 +1367,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120325801</v>
+        <v>120323551</v>
       </c>
       <c r="B8" t="n">
-        <v>57320</v>
+        <v>82321</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1383,39 +1383,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Getklövbäcken, Getklövbäcken, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>578563</v>
+        <v>578374</v>
       </c>
       <c r="R8" t="n">
-        <v>7053248</v>
+        <v>7053367</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1447,7 +1442,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1457,12 +1452,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>16:02</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1477,22 +1467,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120323632</v>
+        <v>120326566</v>
       </c>
       <c r="B9" t="n">
-        <v>78542</v>
+        <v>90864</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1505,21 +1495,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1529,10 +1519,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>578327</v>
+        <v>578709</v>
       </c>
       <c r="R9" t="n">
-        <v>7053358</v>
+        <v>7053176</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1564,7 +1554,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:34</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1574,7 +1564,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:34</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1601,10 +1591,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120323518</v>
+        <v>120326941</v>
       </c>
       <c r="B10" t="n">
-        <v>78542</v>
+        <v>57320</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1617,34 +1607,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Getklövbäcken, Getklövbäcken, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>578469</v>
+        <v>578608</v>
       </c>
       <c r="R10" t="n">
-        <v>7053356</v>
+        <v>7053279</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1676,7 +1671,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1686,7 +1681,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>16:36</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1701,22 +1701,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120325729</v>
+        <v>120326636</v>
       </c>
       <c r="B11" t="n">
-        <v>57320</v>
+        <v>78542</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1729,42 +1729,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Getklövbäcken, Getklövbäcken, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>578537</v>
+        <v>578697</v>
       </c>
       <c r="R11" t="n">
-        <v>7053266</v>
+        <v>7053183</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1796,7 +1788,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1806,7 +1798,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1950,7 +1942,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120325624</v>
+        <v>120324440</v>
       </c>
       <c r="B13" t="n">
         <v>78542</v>
@@ -1990,10 +1982,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>578481</v>
+        <v>578366</v>
       </c>
       <c r="R13" t="n">
-        <v>7053309</v>
+        <v>7053383</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2025,7 +2017,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2035,7 +2027,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2062,10 +2054,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120325831</v>
+        <v>120325729</v>
       </c>
       <c r="B14" t="n">
-        <v>78542</v>
+        <v>57320</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2078,34 +2070,42 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Getklövbäcken, Getklövbäcken, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>578573</v>
+        <v>578537</v>
       </c>
       <c r="R14" t="n">
-        <v>7053238</v>
+        <v>7053266</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2137,7 +2137,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2147,7 +2147,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2174,10 +2174,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120326636</v>
+        <v>120324175</v>
       </c>
       <c r="B15" t="n">
-        <v>78542</v>
+        <v>57320</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2190,21 +2190,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2214,10 +2214,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>578697</v>
+        <v>578371</v>
       </c>
       <c r="R15" t="n">
-        <v>7053183</v>
+        <v>7053353</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2249,7 +2249,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2259,7 +2259,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>15:37</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2286,10 +2291,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120324175</v>
+        <v>120325831</v>
       </c>
       <c r="B16" t="n">
-        <v>57320</v>
+        <v>78542</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2302,21 +2307,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2326,10 +2331,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>578371</v>
+        <v>578573</v>
       </c>
       <c r="R16" t="n">
-        <v>7053353</v>
+        <v>7053238</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2361,7 +2366,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2371,12 +2376,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>15:37</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2403,10 +2403,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120326566</v>
+        <v>120325624</v>
       </c>
       <c r="B17" t="n">
-        <v>90864</v>
+        <v>78542</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2419,21 +2419,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2443,10 +2443,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>578709</v>
+        <v>578481</v>
       </c>
       <c r="R17" t="n">
-        <v>7053176</v>
+        <v>7053309</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2478,7 +2478,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>16:34</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2488,7 +2488,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>16:34</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2515,7 +2515,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120326804</v>
+        <v>120323518</v>
       </c>
       <c r="B18" t="n">
         <v>78542</v>
@@ -2555,10 +2555,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>578652</v>
+        <v>578469</v>
       </c>
       <c r="R18" t="n">
-        <v>7053230</v>
+        <v>7053356</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2590,7 +2590,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2600,7 +2600,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AD18" t="b">

--- a/artfynd/A 44372-2024 artfynd.xlsx
+++ b/artfynd/A 44372-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120323632</v>
+        <v>120323551</v>
       </c>
       <c r="B2" t="n">
-        <v>78542</v>
+        <v>82321</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>578327</v>
+        <v>578374</v>
       </c>
       <c r="R2" t="n">
-        <v>7053358</v>
+        <v>7053367</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,7 +787,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120326804</v>
+        <v>120324440</v>
       </c>
       <c r="B3" t="n">
         <v>78542</v>
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>578652</v>
+        <v>578366</v>
       </c>
       <c r="R3" t="n">
-        <v>7053230</v>
+        <v>7053383</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,7 +899,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120323572</v>
+        <v>120323518</v>
       </c>
       <c r="B4" t="n">
         <v>78542</v>
@@ -939,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>578342</v>
+        <v>578469</v>
       </c>
       <c r="R4" t="n">
-        <v>7053371</v>
+        <v>7053356</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -974,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,7 +1011,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120325801</v>
+        <v>120326941</v>
       </c>
       <c r="B5" t="n">
         <v>57320</v>
@@ -1056,10 +1056,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>578563</v>
+        <v>578608</v>
       </c>
       <c r="R5" t="n">
-        <v>7053248</v>
+        <v>7053279</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1091,7 +1091,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1133,10 +1133,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120325878</v>
+        <v>120325624</v>
       </c>
       <c r="B6" t="n">
-        <v>57320</v>
+        <v>78542</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1149,39 +1149,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Getklövbäcken, Getklövbäcken, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>578640</v>
+        <v>578481</v>
       </c>
       <c r="R6" t="n">
-        <v>7053180</v>
+        <v>7053309</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1213,7 +1208,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1223,12 +1218,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>16:08</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1243,22 +1233,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120326814</v>
+        <v>120323572</v>
       </c>
       <c r="B7" t="n">
-        <v>95225</v>
+        <v>78542</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1267,25 +1257,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2869</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1295,10 +1285,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>578608</v>
+        <v>578342</v>
       </c>
       <c r="R7" t="n">
-        <v>7053279</v>
+        <v>7053371</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1330,7 +1320,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1340,7 +1330,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1355,22 +1345,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120323551</v>
+        <v>120324175</v>
       </c>
       <c r="B8" t="n">
-        <v>82321</v>
+        <v>57320</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1383,21 +1373,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1407,10 +1397,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>578374</v>
+        <v>578371</v>
       </c>
       <c r="R8" t="n">
-        <v>7053367</v>
+        <v>7053353</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1442,7 +1432,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1452,7 +1442,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>15:37</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1479,10 +1474,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120326566</v>
+        <v>120325801</v>
       </c>
       <c r="B9" t="n">
-        <v>90864</v>
+        <v>57320</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1495,34 +1490,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Getklövbäcken, Getklövbäcken, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>578709</v>
+        <v>578563</v>
       </c>
       <c r="R9" t="n">
-        <v>7053176</v>
+        <v>7053248</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1554,7 +1554,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>16:34</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1564,7 +1564,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>16:34</t>
+          <t>16:02</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1579,22 +1584,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120326941</v>
+        <v>120326804</v>
       </c>
       <c r="B10" t="n">
-        <v>57320</v>
+        <v>78542</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1607,39 +1612,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Getklövbäcken, Getklövbäcken, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>578608</v>
+        <v>578652</v>
       </c>
       <c r="R10" t="n">
-        <v>7053279</v>
+        <v>7053230</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1671,7 +1671,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1681,12 +1681,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>16:36</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1701,19 +1696,19 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120326636</v>
+        <v>120325831</v>
       </c>
       <c r="B11" t="n">
         <v>78542</v>
@@ -1753,10 +1748,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>578697</v>
+        <v>578573</v>
       </c>
       <c r="R11" t="n">
-        <v>7053183</v>
+        <v>7053238</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1788,7 +1783,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1798,7 +1793,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1825,10 +1820,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120325418</v>
+        <v>120326636</v>
       </c>
       <c r="B12" t="n">
-        <v>57320</v>
+        <v>78542</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1841,39 +1836,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Getklövbäcken, Getklövbäcken, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>578482</v>
+        <v>578697</v>
       </c>
       <c r="R12" t="n">
-        <v>7053311</v>
+        <v>7053183</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1905,7 +1895,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1915,7 +1905,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1930,22 +1920,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120324440</v>
+        <v>120326566</v>
       </c>
       <c r="B13" t="n">
-        <v>78542</v>
+        <v>90864</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1958,21 +1948,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1982,10 +1972,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>578366</v>
+        <v>578709</v>
       </c>
       <c r="R13" t="n">
-        <v>7053383</v>
+        <v>7053176</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2017,7 +2007,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>16:34</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2027,7 +2017,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>16:34</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2174,7 +2164,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120324175</v>
+        <v>120325878</v>
       </c>
       <c r="B15" t="n">
         <v>57320</v>
@@ -2208,16 +2198,21 @@
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Getklövbäcken, Getklövbäcken, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>578371</v>
+        <v>578640</v>
       </c>
       <c r="R15" t="n">
-        <v>7053353</v>
+        <v>7053180</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2249,7 +2244,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2259,12 +2254,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2279,22 +2274,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120325831</v>
+        <v>120325418</v>
       </c>
       <c r="B16" t="n">
-        <v>78542</v>
+        <v>57320</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2307,34 +2302,39 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Getklövbäcken, Getklövbäcken, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>578573</v>
+        <v>578482</v>
       </c>
       <c r="R16" t="n">
-        <v>7053238</v>
+        <v>7053311</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2366,7 +2366,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2391,22 +2391,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120325624</v>
+        <v>120326814</v>
       </c>
       <c r="B17" t="n">
-        <v>78542</v>
+        <v>95225</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2415,25 +2415,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>2869</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2443,10 +2443,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>578481</v>
+        <v>578608</v>
       </c>
       <c r="R17" t="n">
-        <v>7053309</v>
+        <v>7053279</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2478,7 +2478,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2488,7 +2488,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2503,19 +2503,19 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120323518</v>
+        <v>120323632</v>
       </c>
       <c r="B18" t="n">
         <v>78542</v>
@@ -2555,10 +2555,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>578469</v>
+        <v>578327</v>
       </c>
       <c r="R18" t="n">
-        <v>7053356</v>
+        <v>7053358</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2590,7 +2590,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2600,7 +2600,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AD18" t="b">

--- a/artfynd/A 44372-2024 artfynd.xlsx
+++ b/artfynd/A 44372-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120323551</v>
+        <v>120326636</v>
       </c>
       <c r="B2" t="n">
-        <v>82321</v>
+        <v>78542</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>578374</v>
+        <v>578697</v>
       </c>
       <c r="R2" t="n">
-        <v>7053367</v>
+        <v>7053183</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120324440</v>
+        <v>120323551</v>
       </c>
       <c r="B3" t="n">
-        <v>78542</v>
+        <v>82321</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,21 +803,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>578366</v>
+        <v>578374</v>
       </c>
       <c r="R3" t="n">
-        <v>7053383</v>
+        <v>7053367</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,7 +899,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120323518</v>
+        <v>120325831</v>
       </c>
       <c r="B4" t="n">
         <v>78542</v>
@@ -939,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>578469</v>
+        <v>578573</v>
       </c>
       <c r="R4" t="n">
-        <v>7053356</v>
+        <v>7053238</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -974,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,7 +1011,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120326941</v>
+        <v>120325729</v>
       </c>
       <c r="B5" t="n">
         <v>57320</v>
@@ -1045,21 +1045,24 @@
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
           <t>färska spår</t>
         </is>
       </c>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Getklövbäcken, Getklövbäcken, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>578608</v>
+        <v>578537</v>
       </c>
       <c r="R5" t="n">
-        <v>7053279</v>
+        <v>7053266</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1091,7 +1094,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1101,12 +1104,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>16:36</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1121,12 +1119,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1245,7 +1243,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120323572</v>
+        <v>120326804</v>
       </c>
       <c r="B7" t="n">
         <v>78542</v>
@@ -1285,10 +1283,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>578342</v>
+        <v>578652</v>
       </c>
       <c r="R7" t="n">
-        <v>7053371</v>
+        <v>7053230</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1320,7 +1318,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1330,7 +1328,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1357,10 +1355,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120324175</v>
+        <v>120326814</v>
       </c>
       <c r="B8" t="n">
-        <v>57320</v>
+        <v>95225</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1369,25 +1367,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>2869</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1397,10 +1395,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>578371</v>
+        <v>578608</v>
       </c>
       <c r="R8" t="n">
-        <v>7053353</v>
+        <v>7053279</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1432,7 +1430,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1442,12 +1440,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:37</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1462,12 +1455,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1596,10 +1589,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120326804</v>
+        <v>120326941</v>
       </c>
       <c r="B10" t="n">
-        <v>78542</v>
+        <v>57320</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1612,34 +1605,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Getklövbäcken, Getklövbäcken, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>578652</v>
+        <v>578608</v>
       </c>
       <c r="R10" t="n">
-        <v>7053230</v>
+        <v>7053279</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1671,7 +1669,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1681,7 +1679,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>16:36</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1696,19 +1699,19 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120325831</v>
+        <v>120323632</v>
       </c>
       <c r="B11" t="n">
         <v>78542</v>
@@ -1748,10 +1751,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>578573</v>
+        <v>578327</v>
       </c>
       <c r="R11" t="n">
-        <v>7053238</v>
+        <v>7053358</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1783,7 +1786,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1793,7 +1796,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1820,10 +1823,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120326636</v>
+        <v>120325878</v>
       </c>
       <c r="B12" t="n">
-        <v>78542</v>
+        <v>57320</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1836,34 +1839,39 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Getklövbäcken, Getklövbäcken, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>578697</v>
+        <v>578640</v>
       </c>
       <c r="R12" t="n">
-        <v>7053183</v>
+        <v>7053180</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1895,7 +1903,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1905,7 +1913,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>16:08</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1920,22 +1933,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120326566</v>
+        <v>120324175</v>
       </c>
       <c r="B13" t="n">
-        <v>90864</v>
+        <v>57320</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1948,21 +1961,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1972,10 +1985,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>578709</v>
+        <v>578371</v>
       </c>
       <c r="R13" t="n">
-        <v>7053176</v>
+        <v>7053353</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2007,7 +2020,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>16:34</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2017,7 +2030,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>16:34</t>
+          <t>15:37</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2044,10 +2062,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120325729</v>
+        <v>120323518</v>
       </c>
       <c r="B14" t="n">
-        <v>57320</v>
+        <v>78542</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2060,42 +2078,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Getklövbäcken, Getklövbäcken, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>578537</v>
+        <v>578469</v>
       </c>
       <c r="R14" t="n">
-        <v>7053266</v>
+        <v>7053356</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2127,7 +2137,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2137,7 +2147,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2164,7 +2174,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120325878</v>
+        <v>120325418</v>
       </c>
       <c r="B15" t="n">
         <v>57320</v>
@@ -2209,10 +2219,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>578640</v>
+        <v>578482</v>
       </c>
       <c r="R15" t="n">
-        <v>7053180</v>
+        <v>7053311</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2244,7 +2254,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2254,12 +2264,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>16:08</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2286,10 +2291,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120325418</v>
+        <v>120326566</v>
       </c>
       <c r="B16" t="n">
-        <v>57320</v>
+        <v>90864</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2302,39 +2307,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Getklövbäcken, Getklövbäcken, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>578482</v>
+        <v>578709</v>
       </c>
       <c r="R16" t="n">
-        <v>7053311</v>
+        <v>7053176</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2366,7 +2366,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>16:34</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>16:34</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2391,22 +2391,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120326814</v>
+        <v>120323572</v>
       </c>
       <c r="B17" t="n">
-        <v>95225</v>
+        <v>78542</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2415,25 +2415,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2869</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2443,10 +2443,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>578608</v>
+        <v>578342</v>
       </c>
       <c r="R17" t="n">
-        <v>7053279</v>
+        <v>7053371</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2478,7 +2478,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2488,7 +2488,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2503,19 +2503,19 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120323632</v>
+        <v>120324440</v>
       </c>
       <c r="B18" t="n">
         <v>78542</v>
@@ -2555,10 +2555,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>578327</v>
+        <v>578366</v>
       </c>
       <c r="R18" t="n">
-        <v>7053358</v>
+        <v>7053383</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2590,7 +2590,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2600,7 +2600,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AD18" t="b">

--- a/artfynd/A 44372-2024 artfynd.xlsx
+++ b/artfynd/A 44372-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120326636</v>
+        <v>120323632</v>
       </c>
       <c r="B2" t="n">
         <v>78542</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>578697</v>
+        <v>578327</v>
       </c>
       <c r="R2" t="n">
-        <v>7053183</v>
+        <v>7053358</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120323551</v>
+        <v>120325801</v>
       </c>
       <c r="B3" t="n">
-        <v>82321</v>
+        <v>57320</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,34 +803,39 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Getklövbäcken, Getklövbäcken, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>578374</v>
+        <v>578563</v>
       </c>
       <c r="R3" t="n">
-        <v>7053367</v>
+        <v>7053248</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +877,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>16:02</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -887,19 +897,19 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120325831</v>
+        <v>120323572</v>
       </c>
       <c r="B4" t="n">
         <v>78542</v>
@@ -939,10 +949,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>578573</v>
+        <v>578342</v>
       </c>
       <c r="R4" t="n">
-        <v>7053238</v>
+        <v>7053371</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -974,7 +984,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +994,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,10 +1021,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120325729</v>
+        <v>120323551</v>
       </c>
       <c r="B5" t="n">
-        <v>57320</v>
+        <v>82321</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1027,42 +1037,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Getklövbäcken, Getklövbäcken, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>578537</v>
+        <v>578374</v>
       </c>
       <c r="R5" t="n">
-        <v>7053266</v>
+        <v>7053367</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1094,7 +1096,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1104,7 +1106,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1131,7 +1133,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120325624</v>
+        <v>120323518</v>
       </c>
       <c r="B6" t="n">
         <v>78542</v>
@@ -1171,10 +1173,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>578481</v>
+        <v>578469</v>
       </c>
       <c r="R6" t="n">
-        <v>7053309</v>
+        <v>7053356</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1206,7 +1208,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1216,7 +1218,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1243,10 +1245,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120326804</v>
+        <v>120324175</v>
       </c>
       <c r="B7" t="n">
-        <v>78542</v>
+        <v>57320</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1259,21 +1261,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1283,10 +1285,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>578652</v>
+        <v>578371</v>
       </c>
       <c r="R7" t="n">
-        <v>7053230</v>
+        <v>7053353</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1318,7 +1320,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1328,7 +1330,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>15:37</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1355,10 +1362,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120326814</v>
+        <v>120326636</v>
       </c>
       <c r="B8" t="n">
-        <v>95225</v>
+        <v>78542</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1367,25 +1374,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2869</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1395,10 +1402,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>578608</v>
+        <v>578697</v>
       </c>
       <c r="R8" t="n">
-        <v>7053279</v>
+        <v>7053183</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1430,7 +1437,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1440,7 +1447,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1455,19 +1462,19 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120325801</v>
+        <v>120325878</v>
       </c>
       <c r="B9" t="n">
         <v>57320</v>
@@ -1512,10 +1519,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>578563</v>
+        <v>578640</v>
       </c>
       <c r="R9" t="n">
-        <v>7053248</v>
+        <v>7053180</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1547,7 +1554,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1557,12 +1564,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1589,10 +1596,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120326941</v>
+        <v>120325831</v>
       </c>
       <c r="B10" t="n">
-        <v>57320</v>
+        <v>78542</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1605,39 +1612,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Getklövbäcken, Getklövbäcken, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>578608</v>
+        <v>578573</v>
       </c>
       <c r="R10" t="n">
-        <v>7053279</v>
+        <v>7053238</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1669,7 +1671,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1679,12 +1681,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>16:36</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1699,19 +1696,19 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120323632</v>
+        <v>120324440</v>
       </c>
       <c r="B11" t="n">
         <v>78542</v>
@@ -1751,10 +1748,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>578327</v>
+        <v>578366</v>
       </c>
       <c r="R11" t="n">
-        <v>7053358</v>
+        <v>7053383</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1786,7 +1783,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1796,7 +1793,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1823,10 +1820,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120325878</v>
+        <v>120326814</v>
       </c>
       <c r="B12" t="n">
-        <v>57320</v>
+        <v>95225</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1835,43 +1832,38 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>2869</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Getklövbäcken, Getklövbäcken, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>578640</v>
+        <v>578608</v>
       </c>
       <c r="R12" t="n">
-        <v>7053180</v>
+        <v>7053279</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1903,7 +1895,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1913,12 +1905,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>16:08</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1945,7 +1932,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120324175</v>
+        <v>120326941</v>
       </c>
       <c r="B13" t="n">
         <v>57320</v>
@@ -1979,16 +1966,21 @@
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Getklövbäcken, Getklövbäcken, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>578371</v>
+        <v>578608</v>
       </c>
       <c r="R13" t="n">
-        <v>7053353</v>
+        <v>7053279</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2020,7 +2012,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2030,12 +2022,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2050,19 +2042,19 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120323518</v>
+        <v>120326804</v>
       </c>
       <c r="B14" t="n">
         <v>78542</v>
@@ -2102,10 +2094,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>578469</v>
+        <v>578652</v>
       </c>
       <c r="R14" t="n">
-        <v>7053356</v>
+        <v>7053230</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2137,7 +2129,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2147,7 +2139,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2174,7 +2166,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120325418</v>
+        <v>120325729</v>
       </c>
       <c r="B15" t="n">
         <v>57320</v>
@@ -2208,21 +2200,24 @@
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
           <t>färska spår</t>
         </is>
       </c>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Getklövbäcken, Getklövbäcken, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>578482</v>
+        <v>578537</v>
       </c>
       <c r="R15" t="n">
-        <v>7053311</v>
+        <v>7053266</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2254,7 +2249,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2264,7 +2259,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2279,22 +2274,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120326566</v>
+        <v>120325624</v>
       </c>
       <c r="B16" t="n">
-        <v>90864</v>
+        <v>78542</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2307,21 +2302,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2331,10 +2326,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>578709</v>
+        <v>578481</v>
       </c>
       <c r="R16" t="n">
-        <v>7053176</v>
+        <v>7053309</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2366,7 +2361,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>16:34</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2376,7 +2371,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>16:34</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2403,10 +2398,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120323572</v>
+        <v>120325418</v>
       </c>
       <c r="B17" t="n">
-        <v>78542</v>
+        <v>57320</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2419,34 +2414,39 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Getklövbäcken, Getklövbäcken, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>578342</v>
+        <v>578482</v>
       </c>
       <c r="R17" t="n">
-        <v>7053371</v>
+        <v>7053311</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2478,7 +2478,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2488,7 +2488,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2503,22 +2503,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120324440</v>
+        <v>120326566</v>
       </c>
       <c r="B18" t="n">
-        <v>78542</v>
+        <v>90864</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2531,21 +2531,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2555,10 +2555,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>578366</v>
+        <v>578709</v>
       </c>
       <c r="R18" t="n">
-        <v>7053383</v>
+        <v>7053176</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2590,7 +2590,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>16:34</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2600,7 +2600,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>16:34</t>
         </is>
       </c>
       <c r="AD18" t="b">

--- a/artfynd/A 44372-2024 artfynd.xlsx
+++ b/artfynd/A 44372-2024 artfynd.xlsx
@@ -2054,10 +2054,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120326804</v>
+        <v>120325729</v>
       </c>
       <c r="B14" t="n">
-        <v>78542</v>
+        <v>57320</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2070,34 +2070,42 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Getklövbäcken, Getklövbäcken, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>578652</v>
+        <v>578537</v>
       </c>
       <c r="R14" t="n">
-        <v>7053230</v>
+        <v>7053266</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2129,7 +2137,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2139,7 +2147,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2166,10 +2174,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120325729</v>
+        <v>120326804</v>
       </c>
       <c r="B15" t="n">
-        <v>57320</v>
+        <v>78542</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2182,42 +2190,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Getklövbäcken, Getklövbäcken, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>578537</v>
+        <v>578652</v>
       </c>
       <c r="R15" t="n">
-        <v>7053266</v>
+        <v>7053230</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2249,7 +2249,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2259,7 +2259,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AD15" t="b">

--- a/artfynd/A 44372-2024 artfynd.xlsx
+++ b/artfynd/A 44372-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY18"/>
+  <dimension ref="A1:AY37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2625,6 +2625,2079 @@
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>128313607</v>
+      </c>
+      <c r="B19" t="n">
+        <v>79029</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Getklövbäcken, Getklövbäcken, Ång</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>578334</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7053347</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-09-08</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>18:51</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-09-08</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>18:51</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>128314993</v>
+      </c>
+      <c r="B20" t="n">
+        <v>79029</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Getklövbäcken, Getklövbäcken, Ång</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>578500</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7053339</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-09-08</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>19:45</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-09-08</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>19:45</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>128315431</v>
+      </c>
+      <c r="B21" t="n">
+        <v>91370</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Getklövbäcken, Getklövbäcken, Ång</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>578549</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7053302</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-09-08</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>20:04</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-09-08</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>20:04</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>128315158</v>
+      </c>
+      <c r="B22" t="n">
+        <v>79029</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Getklövbäcken, Getklövbäcken, Ång</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>578531</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7053326</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-09-08</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>19:50</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-09-08</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>19:50</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>128313900</v>
+      </c>
+      <c r="B23" t="n">
+        <v>57672</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Getklövbäcken, Getklövbäcken, Ång</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>578364</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7053346</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-09-08</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>19:05</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-09-08</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>19:05</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>128313672</v>
+      </c>
+      <c r="B24" t="n">
+        <v>98491</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Getklövbäcken, Getklövbäcken, Ång</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>578334</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7053361</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-09-08</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>18:55</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-09-08</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>18:55</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>128313998</v>
+      </c>
+      <c r="B25" t="n">
+        <v>79029</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Getklövbäcken, Getklövbäcken, Ång</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>578359</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7053353</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-09-08</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>19:08</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-09-08</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>19:08</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>128312862</v>
+      </c>
+      <c r="B26" t="n">
+        <v>79029</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Getklövbäcken, Getklövbäcken, Ång</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>578366</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7053291</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-09-08</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>18:23</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-09-08</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>18:23</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>128313227</v>
+      </c>
+      <c r="B27" t="n">
+        <v>79029</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Getklövbäcken, Getklövbäcken, Ång</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>578343</v>
+      </c>
+      <c r="R27" t="n">
+        <v>7053335</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-09-08</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>18:37</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-09-08</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>18:37</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>128315722</v>
+      </c>
+      <c r="B28" t="n">
+        <v>91352</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Getklövbäcken, Getklövbäcken, Ång</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>578585</v>
+      </c>
+      <c r="R28" t="n">
+        <v>7053294</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-09-08</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>20:18</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-09-08</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>20:18</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>128313403</v>
+      </c>
+      <c r="B29" t="n">
+        <v>79029</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Getklövbäcken, Getklövbäcken, Ång</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>578327</v>
+      </c>
+      <c r="R29" t="n">
+        <v>7053341</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-09-08</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>18:43</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-09-08</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>18:43</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>128315521</v>
+      </c>
+      <c r="B30" t="n">
+        <v>79029</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Getklövbäcken, Getklövbäcken, Ång</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>578575</v>
+      </c>
+      <c r="R30" t="n">
+        <v>7053303</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-09-08</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>20:07</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-09-08</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>20:07</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>128313653</v>
+      </c>
+      <c r="B31" t="n">
+        <v>96595</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>2869</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Bollvitmossa</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Sphagnum wulfianum</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Girg.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Getklövbäcken, Getklövbäcken, Ång</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>578333</v>
+      </c>
+      <c r="R31" t="n">
+        <v>7053360</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-09-08</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>18:54</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-09-08</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>18:54</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>128313502</v>
+      </c>
+      <c r="B32" t="n">
+        <v>82870</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>1312</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Getklövbäcken, Getklövbäcken, Ång</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>578334</v>
+      </c>
+      <c r="R32" t="n">
+        <v>7053343</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-09-08</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>18:47</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-09-08</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>18:47</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>128314264</v>
+      </c>
+      <c r="B33" t="n">
+        <v>57672</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Getklövbäcken, Getklövbäcken, Ång</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>578451</v>
+      </c>
+      <c r="R33" t="n">
+        <v>7053343</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2025-09-08</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>19:19</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2025-09-08</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>19:19</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>128312941</v>
+      </c>
+      <c r="B34" t="n">
+        <v>79029</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Getklövbäcken, Getklövbäcken, Ång</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>578353</v>
+      </c>
+      <c r="R34" t="n">
+        <v>7053308</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2025-09-08</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>18:27</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2025-09-08</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>18:27</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>128315753</v>
+      </c>
+      <c r="B35" t="n">
+        <v>91710</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>2062</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Ulltickeporing</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Skeletocutis brevispora</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Niemelä</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Getklövbäcken, Getklövbäcken, Ång</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>578582</v>
+      </c>
+      <c r="R35" t="n">
+        <v>7053292</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2025-09-08</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>20:21</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2025-09-08</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>20:21</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>128315601</v>
+      </c>
+      <c r="B36" t="n">
+        <v>57672</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Getklövbäcken, Getklövbäcken, Ång</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>578562</v>
+      </c>
+      <c r="R36" t="n">
+        <v>7053295</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2025-09-08</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>20:12</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2025-09-08</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>20:12</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>128314896</v>
+      </c>
+      <c r="B37" t="n">
+        <v>57672</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Getklövbäcken, Getklövbäcken, Ång</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>578502</v>
+      </c>
+      <c r="R37" t="n">
+        <v>7053340</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2025-09-08</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>19:42</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2025-09-08</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>19:42</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 44372-2024 artfynd.xlsx
+++ b/artfynd/A 44372-2024 artfynd.xlsx
@@ -3707,7 +3707,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128313403</v>
+        <v>128315521</v>
       </c>
       <c r="B29" t="n">
         <v>79029</v>
@@ -3742,10 +3742,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>578327</v>
+        <v>578575</v>
       </c>
       <c r="R29" t="n">
-        <v>7053341</v>
+        <v>7053303</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3777,7 +3777,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>18:43</t>
+          <t>20:07</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3787,7 +3787,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>18:43</t>
+          <t>20:07</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3814,7 +3814,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128315521</v>
+        <v>128313403</v>
       </c>
       <c r="B30" t="n">
         <v>79029</v>
@@ -3849,10 +3849,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>578575</v>
+        <v>578327</v>
       </c>
       <c r="R30" t="n">
-        <v>7053303</v>
+        <v>7053341</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3884,7 +3884,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>20:07</t>
+          <t>18:43</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3894,7 +3894,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>20:07</t>
+          <t>18:43</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4028,32 +4028,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128313502</v>
+        <v>128315753</v>
       </c>
       <c r="B32" t="n">
-        <v>82870</v>
+        <v>91710</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1312</v>
+        <v>2062</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4063,10 +4063,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>578334</v>
+        <v>578582</v>
       </c>
       <c r="R32" t="n">
-        <v>7053343</v>
+        <v>7053292</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4098,7 +4098,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>18:47</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4108,7 +4108,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>18:47</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4135,10 +4135,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128314264</v>
+        <v>128313502</v>
       </c>
       <c r="B33" t="n">
-        <v>57672</v>
+        <v>82870</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4146,36 +4146,31 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Getklövbäcken, Getklövbäcken, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>578451</v>
+        <v>578334</v>
       </c>
       <c r="R33" t="n">
         <v>7053343</v>
@@ -4210,7 +4205,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>19:19</t>
+          <t>18:47</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4220,12 +4215,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>19:19</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>18:47</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4252,10 +4242,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128312941</v>
+        <v>128314264</v>
       </c>
       <c r="B34" t="n">
-        <v>79029</v>
+        <v>57672</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4263,34 +4253,39 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Getklövbäcken, Getklövbäcken, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>578353</v>
+        <v>578451</v>
       </c>
       <c r="R34" t="n">
-        <v>7053308</v>
+        <v>7053343</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4322,7 +4317,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>18:27</t>
+          <t>19:19</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4332,7 +4327,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>18:27</t>
+          <t>19:19</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4359,32 +4359,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128315753</v>
+        <v>128312941</v>
       </c>
       <c r="B35" t="n">
-        <v>91710</v>
+        <v>79029</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>2062</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4394,10 +4394,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>578582</v>
+        <v>578353</v>
       </c>
       <c r="R35" t="n">
-        <v>7053292</v>
+        <v>7053308</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4429,7 +4429,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>18:27</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4439,7 +4439,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>18:27</t>
         </is>
       </c>
       <c r="AD35" t="b">

--- a/artfynd/A 44372-2024 artfynd.xlsx
+++ b/artfynd/A 44372-2024 artfynd.xlsx
@@ -4028,32 +4028,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128315753</v>
+        <v>128313502</v>
       </c>
       <c r="B32" t="n">
-        <v>91710</v>
+        <v>82870</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>2062</v>
+        <v>1312</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4063,10 +4063,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>578582</v>
+        <v>578334</v>
       </c>
       <c r="R32" t="n">
-        <v>7053292</v>
+        <v>7053343</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4098,7 +4098,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>18:47</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4108,7 +4108,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>18:47</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4135,10 +4135,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128313502</v>
+        <v>128314264</v>
       </c>
       <c r="B33" t="n">
-        <v>82870</v>
+        <v>57672</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4146,31 +4146,36 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Getklövbäcken, Getklövbäcken, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>578334</v>
+        <v>578451</v>
       </c>
       <c r="R33" t="n">
         <v>7053343</v>
@@ -4205,7 +4210,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>18:47</t>
+          <t>19:19</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4215,7 +4220,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>18:47</t>
+          <t>19:19</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4242,10 +4252,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128314264</v>
+        <v>128312941</v>
       </c>
       <c r="B34" t="n">
-        <v>57672</v>
+        <v>79029</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4253,39 +4263,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Getklövbäcken, Getklövbäcken, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>578451</v>
+        <v>578353</v>
       </c>
       <c r="R34" t="n">
-        <v>7053343</v>
+        <v>7053308</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4317,7 +4322,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>19:19</t>
+          <t>18:27</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4327,12 +4332,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>19:19</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>18:27</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4359,32 +4359,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128312941</v>
+        <v>128315753</v>
       </c>
       <c r="B35" t="n">
-        <v>79029</v>
+        <v>91710</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>2062</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4394,10 +4394,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>578353</v>
+        <v>578582</v>
       </c>
       <c r="R35" t="n">
-        <v>7053308</v>
+        <v>7053292</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4429,7 +4429,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>18:27</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4439,7 +4439,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>18:27</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="AD35" t="b">

--- a/artfynd/A 44372-2024 artfynd.xlsx
+++ b/artfynd/A 44372-2024 artfynd.xlsx
@@ -3707,7 +3707,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128315521</v>
+        <v>128313403</v>
       </c>
       <c r="B29" t="n">
         <v>79029</v>
@@ -3742,10 +3742,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>578575</v>
+        <v>578327</v>
       </c>
       <c r="R29" t="n">
-        <v>7053303</v>
+        <v>7053341</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3777,7 +3777,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>20:07</t>
+          <t>18:43</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3787,7 +3787,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>20:07</t>
+          <t>18:43</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3814,7 +3814,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128313403</v>
+        <v>128315521</v>
       </c>
       <c r="B30" t="n">
         <v>79029</v>
@@ -3849,10 +3849,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>578327</v>
+        <v>578575</v>
       </c>
       <c r="R30" t="n">
-        <v>7053341</v>
+        <v>7053303</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3884,7 +3884,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>18:43</t>
+          <t>20:07</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3894,7 +3894,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>18:43</t>
+          <t>20:07</t>
         </is>
       </c>
       <c r="AD30" t="b">

--- a/artfynd/A 44372-2024 artfynd.xlsx
+++ b/artfynd/A 44372-2024 artfynd.xlsx
@@ -2630,7 +2630,7 @@
         <v>128313607</v>
       </c>
       <c r="B19" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2737,7 +2737,7 @@
         <v>128314993</v>
       </c>
       <c r="B20" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2844,7 +2844,7 @@
         <v>128315431</v>
       </c>
       <c r="B21" t="n">
-        <v>91370</v>
+        <v>91378</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2951,7 +2951,7 @@
         <v>128315158</v>
       </c>
       <c r="B22" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3058,7 +3058,7 @@
         <v>128313900</v>
       </c>
       <c r="B23" t="n">
-        <v>57672</v>
+        <v>57673</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3175,7 +3175,7 @@
         <v>128313672</v>
       </c>
       <c r="B24" t="n">
-        <v>98491</v>
+        <v>98499</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3282,7 +3282,7 @@
         <v>128313998</v>
       </c>
       <c r="B25" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3389,7 +3389,7 @@
         <v>128312862</v>
       </c>
       <c r="B26" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3493,10 +3493,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128313227</v>
+        <v>128315722</v>
       </c>
       <c r="B27" t="n">
-        <v>79029</v>
+        <v>91360</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3504,21 +3504,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3528,10 +3528,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>578343</v>
+        <v>578585</v>
       </c>
       <c r="R27" t="n">
-        <v>7053335</v>
+        <v>7053294</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3563,7 +3563,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>18:37</t>
+          <t>20:18</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3573,7 +3573,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>18:37</t>
+          <t>20:18</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3600,10 +3600,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128315722</v>
+        <v>128313227</v>
       </c>
       <c r="B28" t="n">
-        <v>91352</v>
+        <v>79032</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3611,21 +3611,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3635,10 +3635,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>578585</v>
+        <v>578343</v>
       </c>
       <c r="R28" t="n">
-        <v>7053294</v>
+        <v>7053335</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3670,7 +3670,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>20:18</t>
+          <t>18:37</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3680,7 +3680,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>20:18</t>
+          <t>18:37</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3707,10 +3707,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128313403</v>
+        <v>128315521</v>
       </c>
       <c r="B29" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3742,10 +3742,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>578327</v>
+        <v>578575</v>
       </c>
       <c r="R29" t="n">
-        <v>7053341</v>
+        <v>7053303</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3777,7 +3777,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>18:43</t>
+          <t>20:07</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3787,7 +3787,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>18:43</t>
+          <t>20:07</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3814,10 +3814,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128315521</v>
+        <v>128313403</v>
       </c>
       <c r="B30" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3849,10 +3849,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>578575</v>
+        <v>578327</v>
       </c>
       <c r="R30" t="n">
-        <v>7053303</v>
+        <v>7053341</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3884,7 +3884,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>20:07</t>
+          <t>18:43</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3894,7 +3894,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>20:07</t>
+          <t>18:43</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3924,7 +3924,7 @@
         <v>128313653</v>
       </c>
       <c r="B31" t="n">
-        <v>96595</v>
+        <v>96603</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4031,7 +4031,7 @@
         <v>128313502</v>
       </c>
       <c r="B32" t="n">
-        <v>82870</v>
+        <v>82873</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4135,50 +4135,45 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128314264</v>
+        <v>128315753</v>
       </c>
       <c r="B33" t="n">
-        <v>57672</v>
+        <v>91718</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>2062</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Getklövbäcken, Getklövbäcken, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>578451</v>
+        <v>578582</v>
       </c>
       <c r="R33" t="n">
-        <v>7053343</v>
+        <v>7053292</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4210,7 +4205,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>19:19</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4220,12 +4215,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>19:19</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4252,10 +4242,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128312941</v>
+        <v>128314264</v>
       </c>
       <c r="B34" t="n">
-        <v>79029</v>
+        <v>57673</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4263,34 +4253,39 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Getklövbäcken, Getklövbäcken, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>578353</v>
+        <v>578451</v>
       </c>
       <c r="R34" t="n">
-        <v>7053308</v>
+        <v>7053343</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4322,7 +4317,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>18:27</t>
+          <t>19:19</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4332,7 +4327,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>18:27</t>
+          <t>19:19</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4359,32 +4359,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128315753</v>
+        <v>128312941</v>
       </c>
       <c r="B35" t="n">
-        <v>91710</v>
+        <v>79032</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>2062</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4394,10 +4394,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>578582</v>
+        <v>578353</v>
       </c>
       <c r="R35" t="n">
-        <v>7053292</v>
+        <v>7053308</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4429,7 +4429,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>18:27</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4439,7 +4439,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>18:27</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4469,7 +4469,7 @@
         <v>128315601</v>
       </c>
       <c r="B36" t="n">
-        <v>57672</v>
+        <v>57673</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4586,7 +4586,7 @@
         <v>128314896</v>
       </c>
       <c r="B37" t="n">
-        <v>57672</v>
+        <v>57673</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>

--- a/artfynd/A 44372-2024 artfynd.xlsx
+++ b/artfynd/A 44372-2024 artfynd.xlsx
@@ -3493,10 +3493,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128315722</v>
+        <v>128313227</v>
       </c>
       <c r="B27" t="n">
-        <v>91360</v>
+        <v>79032</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3504,21 +3504,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3528,10 +3528,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>578585</v>
+        <v>578343</v>
       </c>
       <c r="R27" t="n">
-        <v>7053294</v>
+        <v>7053335</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3563,7 +3563,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>20:18</t>
+          <t>18:37</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3573,7 +3573,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>20:18</t>
+          <t>18:37</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3600,10 +3600,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128313227</v>
+        <v>128315722</v>
       </c>
       <c r="B28" t="n">
-        <v>79032</v>
+        <v>91360</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3611,21 +3611,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3635,10 +3635,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>578343</v>
+        <v>578585</v>
       </c>
       <c r="R28" t="n">
-        <v>7053335</v>
+        <v>7053294</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3670,7 +3670,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>18:37</t>
+          <t>20:18</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3680,7 +3680,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>18:37</t>
+          <t>20:18</t>
         </is>
       </c>
       <c r="AD28" t="b">

--- a/artfynd/A 44372-2024 artfynd.xlsx
+++ b/artfynd/A 44372-2024 artfynd.xlsx
@@ -2630,7 +2630,7 @@
         <v>128313607</v>
       </c>
       <c r="B19" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2737,7 +2737,7 @@
         <v>128314993</v>
       </c>
       <c r="B20" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2844,7 +2844,7 @@
         <v>128315431</v>
       </c>
       <c r="B21" t="n">
-        <v>91378</v>
+        <v>91470</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2951,7 +2951,7 @@
         <v>128315158</v>
       </c>
       <c r="B22" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3058,7 +3058,7 @@
         <v>128313900</v>
       </c>
       <c r="B23" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3175,7 +3175,7 @@
         <v>128313672</v>
       </c>
       <c r="B24" t="n">
-        <v>98499</v>
+        <v>98592</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3282,7 +3282,7 @@
         <v>128313998</v>
       </c>
       <c r="B25" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3389,7 +3389,7 @@
         <v>128312862</v>
       </c>
       <c r="B26" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3496,7 +3496,7 @@
         <v>128313227</v>
       </c>
       <c r="B27" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3603,7 +3603,7 @@
         <v>128315722</v>
       </c>
       <c r="B28" t="n">
-        <v>91360</v>
+        <v>91452</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3710,7 +3710,7 @@
         <v>128315521</v>
       </c>
       <c r="B29" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3817,7 +3817,7 @@
         <v>128313403</v>
       </c>
       <c r="B30" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3924,7 +3924,7 @@
         <v>128313653</v>
       </c>
       <c r="B31" t="n">
-        <v>96603</v>
+        <v>96696</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4028,32 +4028,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128313502</v>
+        <v>128315753</v>
       </c>
       <c r="B32" t="n">
-        <v>82873</v>
+        <v>91810</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1312</v>
+        <v>2062</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4063,10 +4063,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>578334</v>
+        <v>578582</v>
       </c>
       <c r="R32" t="n">
-        <v>7053343</v>
+        <v>7053292</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4098,7 +4098,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>18:47</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4108,7 +4108,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>18:47</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4135,32 +4135,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128315753</v>
+        <v>128312941</v>
       </c>
       <c r="B33" t="n">
-        <v>91718</v>
+        <v>79083</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>2062</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4170,10 +4170,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>578582</v>
+        <v>578353</v>
       </c>
       <c r="R33" t="n">
-        <v>7053292</v>
+        <v>7053308</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4205,7 +4205,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>18:27</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4215,7 +4215,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>18:27</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4245,7 +4245,7 @@
         <v>128314264</v>
       </c>
       <c r="B34" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4359,10 +4359,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128312941</v>
+        <v>128313502</v>
       </c>
       <c r="B35" t="n">
-        <v>79032</v>
+        <v>82942</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4370,21 +4370,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4394,10 +4394,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>578353</v>
+        <v>578334</v>
       </c>
       <c r="R35" t="n">
-        <v>7053308</v>
+        <v>7053343</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4429,7 +4429,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>18:27</t>
+          <t>18:47</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4439,7 +4439,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>18:27</t>
+          <t>18:47</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4469,7 +4469,7 @@
         <v>128315601</v>
       </c>
       <c r="B36" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4586,7 +4586,7 @@
         <v>128314896</v>
       </c>
       <c r="B37" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>

--- a/artfynd/A 44372-2024 artfynd.xlsx
+++ b/artfynd/A 44372-2024 artfynd.xlsx
@@ -3493,10 +3493,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128313227</v>
+        <v>128315722</v>
       </c>
       <c r="B27" t="n">
-        <v>79083</v>
+        <v>91452</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3504,21 +3504,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3528,10 +3528,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>578343</v>
+        <v>578585</v>
       </c>
       <c r="R27" t="n">
-        <v>7053335</v>
+        <v>7053294</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3563,7 +3563,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>18:37</t>
+          <t>20:18</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3573,7 +3573,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>18:37</t>
+          <t>20:18</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3600,10 +3600,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128315722</v>
+        <v>128313227</v>
       </c>
       <c r="B28" t="n">
-        <v>91452</v>
+        <v>79083</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3611,21 +3611,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3635,10 +3635,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>578585</v>
+        <v>578343</v>
       </c>
       <c r="R28" t="n">
-        <v>7053294</v>
+        <v>7053335</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3670,7 +3670,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>20:18</t>
+          <t>18:37</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3680,7 +3680,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>20:18</t>
+          <t>18:37</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4028,32 +4028,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128315753</v>
+        <v>128313502</v>
       </c>
       <c r="B32" t="n">
-        <v>91810</v>
+        <v>82942</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>2062</v>
+        <v>1312</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4063,10 +4063,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>578582</v>
+        <v>578334</v>
       </c>
       <c r="R32" t="n">
-        <v>7053292</v>
+        <v>7053343</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4098,7 +4098,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>18:47</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4108,7 +4108,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>18:47</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4135,32 +4135,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128312941</v>
+        <v>128315753</v>
       </c>
       <c r="B33" t="n">
-        <v>79083</v>
+        <v>91810</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>2062</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4170,10 +4170,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>578353</v>
+        <v>578582</v>
       </c>
       <c r="R33" t="n">
-        <v>7053308</v>
+        <v>7053292</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4205,7 +4205,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>18:27</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4215,7 +4215,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>18:27</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4242,10 +4242,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128314264</v>
+        <v>128312941</v>
       </c>
       <c r="B34" t="n">
-        <v>57685</v>
+        <v>79083</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4253,39 +4253,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Getklövbäcken, Getklövbäcken, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>578451</v>
+        <v>578353</v>
       </c>
       <c r="R34" t="n">
-        <v>7053343</v>
+        <v>7053308</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4317,7 +4312,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>19:19</t>
+          <t>18:27</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4327,12 +4322,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>19:19</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>18:27</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4359,10 +4349,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128313502</v>
+        <v>128314264</v>
       </c>
       <c r="B35" t="n">
-        <v>82942</v>
+        <v>57685</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4370,31 +4360,36 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Getklövbäcken, Getklövbäcken, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>578334</v>
+        <v>578451</v>
       </c>
       <c r="R35" t="n">
         <v>7053343</v>
@@ -4429,7 +4424,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>18:47</t>
+          <t>19:19</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4439,7 +4434,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>18:47</t>
+          <t>19:19</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD35" t="b">

--- a/artfynd/A 44372-2024 artfynd.xlsx
+++ b/artfynd/A 44372-2024 artfynd.xlsx
@@ -3055,50 +3055,45 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128313900</v>
+        <v>128313672</v>
       </c>
       <c r="B23" t="n">
-        <v>57685</v>
+        <v>98592</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Getklövbäcken, Getklövbäcken, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>578364</v>
+        <v>578334</v>
       </c>
       <c r="R23" t="n">
-        <v>7053346</v>
+        <v>7053361</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3130,7 +3125,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>19:05</t>
+          <t>18:55</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3140,12 +3135,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>19:05</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>18:55</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3172,45 +3162,50 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128313672</v>
+        <v>128313900</v>
       </c>
       <c r="B24" t="n">
-        <v>98592</v>
+        <v>57685</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Getklövbäcken, Getklövbäcken, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>578334</v>
+        <v>578364</v>
       </c>
       <c r="R24" t="n">
-        <v>7053361</v>
+        <v>7053346</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3242,7 +3237,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>18:55</t>
+          <t>19:05</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3252,7 +3247,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>18:55</t>
+          <t>19:05</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3493,10 +3493,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128315722</v>
+        <v>128313227</v>
       </c>
       <c r="B27" t="n">
-        <v>91452</v>
+        <v>79083</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3504,21 +3504,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3528,10 +3528,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>578585</v>
+        <v>578343</v>
       </c>
       <c r="R27" t="n">
-        <v>7053294</v>
+        <v>7053335</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3563,7 +3563,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>20:18</t>
+          <t>18:37</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3573,7 +3573,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>20:18</t>
+          <t>18:37</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3600,10 +3600,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128313227</v>
+        <v>128315722</v>
       </c>
       <c r="B28" t="n">
-        <v>79083</v>
+        <v>91452</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3611,21 +3611,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3635,10 +3635,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>578343</v>
+        <v>578585</v>
       </c>
       <c r="R28" t="n">
-        <v>7053335</v>
+        <v>7053294</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3670,7 +3670,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>18:37</t>
+          <t>20:18</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3680,7 +3680,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>18:37</t>
+          <t>20:18</t>
         </is>
       </c>
       <c r="AD28" t="b">

--- a/artfynd/A 44372-2024 artfynd.xlsx
+++ b/artfynd/A 44372-2024 artfynd.xlsx
@@ -2630,7 +2630,7 @@
         <v>128313607</v>
       </c>
       <c r="B19" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2737,7 +2737,7 @@
         <v>128314993</v>
       </c>
       <c r="B20" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2844,7 +2844,7 @@
         <v>128315431</v>
       </c>
       <c r="B21" t="n">
-        <v>91470</v>
+        <v>91482</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2951,7 +2951,7 @@
         <v>128315158</v>
       </c>
       <c r="B22" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3055,45 +3055,50 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128313672</v>
+        <v>128313900</v>
       </c>
       <c r="B23" t="n">
-        <v>98592</v>
+        <v>57689</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Getklövbäcken, Getklövbäcken, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>578334</v>
+        <v>578364</v>
       </c>
       <c r="R23" t="n">
-        <v>7053361</v>
+        <v>7053346</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3125,7 +3130,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>18:55</t>
+          <t>19:05</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3135,7 +3140,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>18:55</t>
+          <t>19:05</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3162,50 +3172,45 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128313900</v>
+        <v>128313672</v>
       </c>
       <c r="B24" t="n">
-        <v>57685</v>
+        <v>98606</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Getklövbäcken, Getklövbäcken, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>578364</v>
+        <v>578334</v>
       </c>
       <c r="R24" t="n">
-        <v>7053346</v>
+        <v>7053361</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3237,7 +3242,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>19:05</t>
+          <t>18:55</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3247,12 +3252,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>19:05</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>18:55</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3282,7 +3282,7 @@
         <v>128313998</v>
       </c>
       <c r="B25" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3389,7 +3389,7 @@
         <v>128312862</v>
       </c>
       <c r="B26" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3493,10 +3493,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128313227</v>
+        <v>128315722</v>
       </c>
       <c r="B27" t="n">
-        <v>79083</v>
+        <v>91464</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3504,21 +3504,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3528,10 +3528,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>578343</v>
+        <v>578585</v>
       </c>
       <c r="R27" t="n">
-        <v>7053335</v>
+        <v>7053294</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3563,7 +3563,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>18:37</t>
+          <t>20:18</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3573,7 +3573,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>18:37</t>
+          <t>20:18</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3600,10 +3600,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128315722</v>
+        <v>128313227</v>
       </c>
       <c r="B28" t="n">
-        <v>91452</v>
+        <v>79087</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3611,21 +3611,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3635,10 +3635,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>578585</v>
+        <v>578343</v>
       </c>
       <c r="R28" t="n">
-        <v>7053294</v>
+        <v>7053335</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3670,7 +3670,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>20:18</t>
+          <t>18:37</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3680,7 +3680,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>20:18</t>
+          <t>18:37</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3707,10 +3707,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128315521</v>
+        <v>128313403</v>
       </c>
       <c r="B29" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3742,10 +3742,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>578575</v>
+        <v>578327</v>
       </c>
       <c r="R29" t="n">
-        <v>7053303</v>
+        <v>7053341</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3777,7 +3777,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>20:07</t>
+          <t>18:43</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3787,7 +3787,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>20:07</t>
+          <t>18:43</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3814,10 +3814,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128313403</v>
+        <v>128315521</v>
       </c>
       <c r="B30" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3849,10 +3849,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>578327</v>
+        <v>578575</v>
       </c>
       <c r="R30" t="n">
-        <v>7053341</v>
+        <v>7053303</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3884,7 +3884,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>18:43</t>
+          <t>20:07</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3894,7 +3894,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>18:43</t>
+          <t>20:07</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3924,7 +3924,7 @@
         <v>128313653</v>
       </c>
       <c r="B31" t="n">
-        <v>96696</v>
+        <v>96708</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4028,10 +4028,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128313502</v>
+        <v>128314264</v>
       </c>
       <c r="B32" t="n">
-        <v>82942</v>
+        <v>57689</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4039,31 +4039,36 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Getklövbäcken, Getklövbäcken, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>578334</v>
+        <v>578451</v>
       </c>
       <c r="R32" t="n">
         <v>7053343</v>
@@ -4098,7 +4103,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>18:47</t>
+          <t>19:19</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4108,7 +4113,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>18:47</t>
+          <t>19:19</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4135,32 +4145,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128315753</v>
+        <v>128312941</v>
       </c>
       <c r="B33" t="n">
-        <v>91810</v>
+        <v>79087</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>2062</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4170,10 +4180,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>578582</v>
+        <v>578353</v>
       </c>
       <c r="R33" t="n">
-        <v>7053292</v>
+        <v>7053308</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4205,7 +4215,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>18:27</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4215,7 +4225,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>18:27</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4242,10 +4252,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128312941</v>
+        <v>128313502</v>
       </c>
       <c r="B34" t="n">
-        <v>79083</v>
+        <v>82946</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4253,21 +4263,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4277,10 +4287,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>578353</v>
+        <v>578334</v>
       </c>
       <c r="R34" t="n">
-        <v>7053308</v>
+        <v>7053343</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4312,7 +4322,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>18:27</t>
+          <t>18:47</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4322,7 +4332,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>18:27</t>
+          <t>18:47</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4349,50 +4359,45 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128314264</v>
+        <v>128315753</v>
       </c>
       <c r="B35" t="n">
-        <v>57685</v>
+        <v>91822</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>2062</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Getklövbäcken, Getklövbäcken, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>578451</v>
+        <v>578582</v>
       </c>
       <c r="R35" t="n">
-        <v>7053343</v>
+        <v>7053292</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4424,7 +4429,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>19:19</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4434,12 +4439,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>19:19</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4469,7 +4469,7 @@
         <v>128315601</v>
       </c>
       <c r="B36" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4586,7 +4586,7 @@
         <v>128314896</v>
       </c>
       <c r="B37" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>

--- a/artfynd/A 44372-2024 artfynd.xlsx
+++ b/artfynd/A 44372-2024 artfynd.xlsx
@@ -2630,7 +2630,7 @@
         <v>128313607</v>
       </c>
       <c r="B19" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2737,7 +2737,7 @@
         <v>128314993</v>
       </c>
       <c r="B20" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2844,7 +2844,7 @@
         <v>128315431</v>
       </c>
       <c r="B21" t="n">
-        <v>91482</v>
+        <v>91484</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2951,7 +2951,7 @@
         <v>128315158</v>
       </c>
       <c r="B22" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3055,50 +3055,45 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128313900</v>
+        <v>128313672</v>
       </c>
       <c r="B23" t="n">
-        <v>57689</v>
+        <v>98609</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Getklövbäcken, Getklövbäcken, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>578364</v>
+        <v>578334</v>
       </c>
       <c r="R23" t="n">
-        <v>7053346</v>
+        <v>7053361</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3130,7 +3125,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>19:05</t>
+          <t>18:55</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3140,12 +3135,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>19:05</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>18:55</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3172,45 +3162,50 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128313672</v>
+        <v>128313900</v>
       </c>
       <c r="B24" t="n">
-        <v>98606</v>
+        <v>57689</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Getklövbäcken, Getklövbäcken, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>578334</v>
+        <v>578364</v>
       </c>
       <c r="R24" t="n">
-        <v>7053361</v>
+        <v>7053346</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3242,7 +3237,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>18:55</t>
+          <t>19:05</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3252,7 +3247,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>18:55</t>
+          <t>19:05</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3282,7 +3282,7 @@
         <v>128313998</v>
       </c>
       <c r="B25" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3389,7 +3389,7 @@
         <v>128312862</v>
       </c>
       <c r="B26" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3496,7 +3496,7 @@
         <v>128315722</v>
       </c>
       <c r="B27" t="n">
-        <v>91464</v>
+        <v>91466</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3603,7 +3603,7 @@
         <v>128313227</v>
       </c>
       <c r="B28" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3707,10 +3707,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128313403</v>
+        <v>128315521</v>
       </c>
       <c r="B29" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3742,10 +3742,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>578327</v>
+        <v>578575</v>
       </c>
       <c r="R29" t="n">
-        <v>7053341</v>
+        <v>7053303</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3777,7 +3777,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>18:43</t>
+          <t>20:07</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3787,7 +3787,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>18:43</t>
+          <t>20:07</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3814,10 +3814,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128315521</v>
+        <v>128313403</v>
       </c>
       <c r="B30" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3849,10 +3849,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>578575</v>
+        <v>578327</v>
       </c>
       <c r="R30" t="n">
-        <v>7053303</v>
+        <v>7053341</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3884,7 +3884,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>20:07</t>
+          <t>18:43</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3894,7 +3894,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>20:07</t>
+          <t>18:43</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3924,7 +3924,7 @@
         <v>128313653</v>
       </c>
       <c r="B31" t="n">
-        <v>96708</v>
+        <v>96710</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4028,10 +4028,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128314264</v>
+        <v>128312941</v>
       </c>
       <c r="B32" t="n">
-        <v>57689</v>
+        <v>79089</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4039,39 +4039,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Getklövbäcken, Getklövbäcken, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>578451</v>
+        <v>578353</v>
       </c>
       <c r="R32" t="n">
-        <v>7053343</v>
+        <v>7053308</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4103,7 +4098,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>19:19</t>
+          <t>18:27</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4113,12 +4108,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>19:19</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>18:27</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4145,10 +4135,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128312941</v>
+        <v>128314264</v>
       </c>
       <c r="B33" t="n">
-        <v>79087</v>
+        <v>57689</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4156,34 +4146,39 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Getklövbäcken, Getklövbäcken, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>578353</v>
+        <v>578451</v>
       </c>
       <c r="R33" t="n">
-        <v>7053308</v>
+        <v>7053343</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4215,7 +4210,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>18:27</t>
+          <t>19:19</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4225,7 +4220,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>18:27</t>
+          <t>19:19</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4255,7 +4255,7 @@
         <v>128313502</v>
       </c>
       <c r="B34" t="n">
-        <v>82946</v>
+        <v>82948</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4362,7 +4362,7 @@
         <v>128315753</v>
       </c>
       <c r="B35" t="n">
-        <v>91822</v>
+        <v>91824</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>

--- a/artfynd/A 44372-2024 artfynd.xlsx
+++ b/artfynd/A 44372-2024 artfynd.xlsx
@@ -3055,45 +3055,50 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128313672</v>
+        <v>128313900</v>
       </c>
       <c r="B23" t="n">
-        <v>98609</v>
+        <v>57689</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Getklövbäcken, Getklövbäcken, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>578334</v>
+        <v>578364</v>
       </c>
       <c r="R23" t="n">
-        <v>7053361</v>
+        <v>7053346</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3125,7 +3130,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>18:55</t>
+          <t>19:05</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3135,7 +3140,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>18:55</t>
+          <t>19:05</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3162,50 +3172,45 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128313900</v>
+        <v>128313672</v>
       </c>
       <c r="B24" t="n">
-        <v>57689</v>
+        <v>98612</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Getklövbäcken, Getklövbäcken, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>578364</v>
+        <v>578334</v>
       </c>
       <c r="R24" t="n">
-        <v>7053346</v>
+        <v>7053361</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3237,7 +3242,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>19:05</t>
+          <t>18:55</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3247,12 +3252,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>19:05</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>18:55</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -4028,10 +4028,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128312941</v>
+        <v>128313502</v>
       </c>
       <c r="B32" t="n">
-        <v>79089</v>
+        <v>82948</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4039,21 +4039,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4063,10 +4063,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>578353</v>
+        <v>578334</v>
       </c>
       <c r="R32" t="n">
-        <v>7053308</v>
+        <v>7053343</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4098,7 +4098,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>18:27</t>
+          <t>18:47</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4108,7 +4108,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>18:27</t>
+          <t>18:47</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4135,10 +4135,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128314264</v>
+        <v>128312941</v>
       </c>
       <c r="B33" t="n">
-        <v>57689</v>
+        <v>79089</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4146,39 +4146,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Getklövbäcken, Getklövbäcken, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>578451</v>
+        <v>578353</v>
       </c>
       <c r="R33" t="n">
-        <v>7053343</v>
+        <v>7053308</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4210,7 +4205,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>19:19</t>
+          <t>18:27</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4220,12 +4215,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>19:19</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>18:27</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4252,10 +4242,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128313502</v>
+        <v>128314264</v>
       </c>
       <c r="B34" t="n">
-        <v>82948</v>
+        <v>57689</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4263,31 +4253,36 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Getklövbäcken, Getklövbäcken, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>578334</v>
+        <v>578451</v>
       </c>
       <c r="R34" t="n">
         <v>7053343</v>
@@ -4322,7 +4317,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>18:47</t>
+          <t>19:19</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4332,7 +4327,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>18:47</t>
+          <t>19:19</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD34" t="b">

--- a/artfynd/A 44372-2024 artfynd.xlsx
+++ b/artfynd/A 44372-2024 artfynd.xlsx
@@ -2844,7 +2844,7 @@
         <v>128315431</v>
       </c>
       <c r="B21" t="n">
-        <v>91484</v>
+        <v>91485</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3175,7 +3175,7 @@
         <v>128313672</v>
       </c>
       <c r="B24" t="n">
-        <v>98612</v>
+        <v>98613</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3496,7 +3496,7 @@
         <v>128315722</v>
       </c>
       <c r="B27" t="n">
-        <v>91466</v>
+        <v>91467</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3924,7 +3924,7 @@
         <v>128313653</v>
       </c>
       <c r="B31" t="n">
-        <v>96710</v>
+        <v>96711</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4028,10 +4028,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128313502</v>
+        <v>128312941</v>
       </c>
       <c r="B32" t="n">
-        <v>82948</v>
+        <v>79089</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4039,21 +4039,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4063,10 +4063,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>578334</v>
+        <v>578353</v>
       </c>
       <c r="R32" t="n">
-        <v>7053343</v>
+        <v>7053308</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4098,7 +4098,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>18:47</t>
+          <t>18:27</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4108,7 +4108,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>18:47</t>
+          <t>18:27</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4135,10 +4135,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128312941</v>
+        <v>128314264</v>
       </c>
       <c r="B33" t="n">
-        <v>79089</v>
+        <v>57689</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4146,34 +4146,39 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Getklövbäcken, Getklövbäcken, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>578353</v>
+        <v>578451</v>
       </c>
       <c r="R33" t="n">
-        <v>7053308</v>
+        <v>7053343</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4205,7 +4210,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>18:27</t>
+          <t>19:19</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4215,7 +4220,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>18:27</t>
+          <t>19:19</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4242,10 +4252,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128314264</v>
+        <v>128313502</v>
       </c>
       <c r="B34" t="n">
-        <v>57689</v>
+        <v>82948</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4253,36 +4263,31 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Getklövbäcken, Getklövbäcken, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>578451</v>
+        <v>578334</v>
       </c>
       <c r="R34" t="n">
         <v>7053343</v>
@@ -4317,7 +4322,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>19:19</t>
+          <t>18:47</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4327,12 +4332,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>19:19</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>18:47</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4362,7 +4362,7 @@
         <v>128315753</v>
       </c>
       <c r="B35" t="n">
-        <v>91824</v>
+        <v>91825</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>

--- a/artfynd/A 44372-2024 artfynd.xlsx
+++ b/artfynd/A 44372-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY37"/>
+  <dimension ref="A1:AY62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4028,10 +4028,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128312941</v>
+        <v>128313502</v>
       </c>
       <c r="B32" t="n">
-        <v>79089</v>
+        <v>82948</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4039,21 +4039,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4063,10 +4063,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>578353</v>
+        <v>578334</v>
       </c>
       <c r="R32" t="n">
-        <v>7053308</v>
+        <v>7053343</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4098,7 +4098,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>18:27</t>
+          <t>18:47</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4108,7 +4108,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>18:27</t>
+          <t>18:47</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4252,10 +4252,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128313502</v>
+        <v>128312941</v>
       </c>
       <c r="B34" t="n">
-        <v>82948</v>
+        <v>79089</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4263,21 +4263,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4287,10 +4287,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>578334</v>
+        <v>578353</v>
       </c>
       <c r="R34" t="n">
-        <v>7053343</v>
+        <v>7053308</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4322,7 +4322,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>18:47</t>
+          <t>18:27</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4332,7 +4332,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>18:47</t>
+          <t>18:27</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4698,6 +4698,2722 @@
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>128828362</v>
+      </c>
+      <c r="B38" t="n">
+        <v>91695</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>48</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Lappticka</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Amylocystis lapponica</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Romell) Bondartsev &amp; Singer</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Getklövbäcken, Getklövbäcken, Ång</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>578684</v>
+      </c>
+      <c r="R38" t="n">
+        <v>7053109</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>16:55</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>16:55</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>128827795</v>
+      </c>
+      <c r="B39" t="n">
+        <v>79116</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Getklövbäcken, Getklövbäcken, Ång</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>578718</v>
+      </c>
+      <c r="R39" t="n">
+        <v>7053164</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>16:31</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>16:31</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>128826746</v>
+      </c>
+      <c r="B40" t="n">
+        <v>79116</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Getklövbäcken, Getklövbäcken, Ång</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>578626</v>
+      </c>
+      <c r="R40" t="n">
+        <v>7053261</v>
+      </c>
+      <c r="S40" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>15:43</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>15:43</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>128826730</v>
+      </c>
+      <c r="B41" t="n">
+        <v>92818</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Getklövbäcken, Getklövbäcken, Ång</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>578639</v>
+      </c>
+      <c r="R41" t="n">
+        <v>7053260</v>
+      </c>
+      <c r="S41" t="n">
+        <v>10</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>15:42</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>15:42</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF41" t="inlineStr"/>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>128827960</v>
+      </c>
+      <c r="B42" t="n">
+        <v>91494</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Getklövbäcken, Getklövbäcken, Ång</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>578713</v>
+      </c>
+      <c r="R42" t="n">
+        <v>7053139</v>
+      </c>
+      <c r="S42" t="n">
+        <v>10</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>16:39</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>16:39</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>128826443</v>
+      </c>
+      <c r="B43" t="n">
+        <v>96738</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>2869</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Bollvitmossa</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Sphagnum wulfianum</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Girg.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Getklövbäcken, Getklövbäcken, Ång</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>578601</v>
+      </c>
+      <c r="R43" t="n">
+        <v>7053281</v>
+      </c>
+      <c r="S43" t="n">
+        <v>10</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>15:29</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>15:29</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>128826236</v>
+      </c>
+      <c r="B44" t="n">
+        <v>91494</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Getklövbäcken, Getklövbäcken, Ång</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>578567</v>
+      </c>
+      <c r="R44" t="n">
+        <v>7053297</v>
+      </c>
+      <c r="S44" t="n">
+        <v>10</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>15:24</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>15:24</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>128827105</v>
+      </c>
+      <c r="B45" t="n">
+        <v>91494</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Getklövbäcken, Getklövbäcken, Ång</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>578667</v>
+      </c>
+      <c r="R45" t="n">
+        <v>7053226</v>
+      </c>
+      <c r="S45" t="n">
+        <v>10</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>15:57</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>15:57</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>128828240</v>
+      </c>
+      <c r="B46" t="n">
+        <v>57716</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Getklövbäcken, Getklövbäcken, Ång</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>578689</v>
+      </c>
+      <c r="R46" t="n">
+        <v>7053119</v>
+      </c>
+      <c r="S46" t="n">
+        <v>10</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>16:50</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>16:50</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>128828029</v>
+      </c>
+      <c r="B47" t="n">
+        <v>91790</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>658</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Rhodofomes roseus</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Getklövbäcken, Getklövbäcken, Ång</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>578708</v>
+      </c>
+      <c r="R47" t="n">
+        <v>7053135</v>
+      </c>
+      <c r="S47" t="n">
+        <v>10</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>16:41</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>16:41</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>128827291</v>
+      </c>
+      <c r="B48" t="n">
+        <v>98619</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Getklövbäcken, Getklövbäcken, Ång</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>578691</v>
+      </c>
+      <c r="R48" t="n">
+        <v>7053218</v>
+      </c>
+      <c r="S48" t="n">
+        <v>10</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>128827406</v>
+      </c>
+      <c r="B49" t="n">
+        <v>79116</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Getklövbäcken, Getklövbäcken, Ång</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>578698</v>
+      </c>
+      <c r="R49" t="n">
+        <v>7053194</v>
+      </c>
+      <c r="S49" t="n">
+        <v>10</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>128828721</v>
+      </c>
+      <c r="B50" t="n">
+        <v>96738</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>2869</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Bollvitmossa</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Sphagnum wulfianum</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Girg.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Getklövbäcken, Getklövbäcken, Ång</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>578692</v>
+      </c>
+      <c r="R50" t="n">
+        <v>7053146</v>
+      </c>
+      <c r="S50" t="n">
+        <v>10</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>17:08</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>17:08</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>128827329</v>
+      </c>
+      <c r="B51" t="n">
+        <v>82975</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>1312</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Getklövbäcken, Getklövbäcken, Ång</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>578686</v>
+      </c>
+      <c r="R51" t="n">
+        <v>7053219</v>
+      </c>
+      <c r="S51" t="n">
+        <v>10</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>16:10</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>16:10</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>128826703</v>
+      </c>
+      <c r="B52" t="n">
+        <v>57876</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Getklövbäcken, Getklövbäcken, Ång</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>578633</v>
+      </c>
+      <c r="R52" t="n">
+        <v>7053264</v>
+      </c>
+      <c r="S52" t="n">
+        <v>10</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>15:40</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>15:40</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>128827904</v>
+      </c>
+      <c r="B53" t="n">
+        <v>79116</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Getklövbäcken, Getklövbäcken, Ång</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>578704</v>
+      </c>
+      <c r="R53" t="n">
+        <v>7053152</v>
+      </c>
+      <c r="S53" t="n">
+        <v>10</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>16:36</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>16:36</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>128826854</v>
+      </c>
+      <c r="B54" t="n">
+        <v>82975</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>1312</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Getklövbäcken, Getklövbäcken, Ång</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>578630</v>
+      </c>
+      <c r="R54" t="n">
+        <v>7053254</v>
+      </c>
+      <c r="S54" t="n">
+        <v>10</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>15:47</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>15:47</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>128830025</v>
+      </c>
+      <c r="B55" t="n">
+        <v>91512</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Getklövbäcken, Getklövbäcken, Ång</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>578643</v>
+      </c>
+      <c r="R55" t="n">
+        <v>7053222</v>
+      </c>
+      <c r="S55" t="n">
+        <v>10</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>17:36</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>17:36</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>128830607</v>
+      </c>
+      <c r="B56" t="n">
+        <v>91512</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Getklövbäcken, Getklövbäcken, Ång</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>578554</v>
+      </c>
+      <c r="R56" t="n">
+        <v>7053252</v>
+      </c>
+      <c r="S56" t="n">
+        <v>10</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>17:45</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>17:45</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>128827117</v>
+      </c>
+      <c r="B57" t="n">
+        <v>79116</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Getklövbäcken, Getklövbäcken, Ång</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>578673</v>
+      </c>
+      <c r="R57" t="n">
+        <v>7053215</v>
+      </c>
+      <c r="S57" t="n">
+        <v>10</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>15:58</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>15:58</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>128827181</v>
+      </c>
+      <c r="B58" t="n">
+        <v>57716</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Getklövbäcken, Getklövbäcken, Ång</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>578677</v>
+      </c>
+      <c r="R58" t="n">
+        <v>7053213</v>
+      </c>
+      <c r="S58" t="n">
+        <v>10</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>128827078</v>
+      </c>
+      <c r="B59" t="n">
+        <v>79116</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Getklövbäcken, Getklövbäcken, Ång</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>578658</v>
+      </c>
+      <c r="R59" t="n">
+        <v>7053224</v>
+      </c>
+      <c r="S59" t="n">
+        <v>10</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>15:55</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>15:55</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>128826680</v>
+      </c>
+      <c r="B60" t="n">
+        <v>79116</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Getklövbäcken, Getklövbäcken, Ång</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>578621</v>
+      </c>
+      <c r="R60" t="n">
+        <v>7053263</v>
+      </c>
+      <c r="S60" t="n">
+        <v>10</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>15:39</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>15:39</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>128828903</v>
+      </c>
+      <c r="B61" t="n">
+        <v>79116</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Getklövbäcken, Getklövbäcken, Ång</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>578689</v>
+      </c>
+      <c r="R61" t="n">
+        <v>7053183</v>
+      </c>
+      <c r="S61" t="n">
+        <v>10</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>17:15</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>17:15</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>128829015</v>
+      </c>
+      <c r="B62" t="n">
+        <v>98619</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Getklövbäcken, Getklövbäcken, Ång</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>578684</v>
+      </c>
+      <c r="R62" t="n">
+        <v>7053174</v>
+      </c>
+      <c r="S62" t="n">
+        <v>10</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>17:19</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>17:19</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 44372-2024 artfynd.xlsx
+++ b/artfynd/A 44372-2024 artfynd.xlsx
@@ -2630,7 +2630,7 @@
         <v>128313607</v>
       </c>
       <c r="B19" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2737,7 +2737,7 @@
         <v>128314993</v>
       </c>
       <c r="B20" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2844,7 +2844,7 @@
         <v>128315431</v>
       </c>
       <c r="B21" t="n">
-        <v>91485</v>
+        <v>91512</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2951,7 +2951,7 @@
         <v>128315158</v>
       </c>
       <c r="B22" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3058,7 +3058,7 @@
         <v>128313900</v>
       </c>
       <c r="B23" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3175,7 +3175,7 @@
         <v>128313672</v>
       </c>
       <c r="B24" t="n">
-        <v>98613</v>
+        <v>98640</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3282,7 +3282,7 @@
         <v>128313998</v>
       </c>
       <c r="B25" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3389,7 +3389,7 @@
         <v>128312862</v>
       </c>
       <c r="B26" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3493,10 +3493,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128315722</v>
+        <v>128313227</v>
       </c>
       <c r="B27" t="n">
-        <v>91467</v>
+        <v>79116</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3504,21 +3504,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3528,10 +3528,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>578585</v>
+        <v>578343</v>
       </c>
       <c r="R27" t="n">
-        <v>7053294</v>
+        <v>7053335</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3563,7 +3563,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>20:18</t>
+          <t>18:37</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3573,7 +3573,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>20:18</t>
+          <t>18:37</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3600,10 +3600,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128313227</v>
+        <v>128315722</v>
       </c>
       <c r="B28" t="n">
-        <v>79089</v>
+        <v>91494</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3611,21 +3611,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3635,10 +3635,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>578343</v>
+        <v>578585</v>
       </c>
       <c r="R28" t="n">
-        <v>7053335</v>
+        <v>7053294</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3670,7 +3670,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>18:37</t>
+          <t>20:18</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3680,7 +3680,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>18:37</t>
+          <t>20:18</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3710,7 +3710,7 @@
         <v>128315521</v>
       </c>
       <c r="B29" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3817,7 +3817,7 @@
         <v>128313403</v>
       </c>
       <c r="B30" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3924,7 +3924,7 @@
         <v>128313653</v>
       </c>
       <c r="B31" t="n">
-        <v>96711</v>
+        <v>96738</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4031,7 +4031,7 @@
         <v>128313502</v>
       </c>
       <c r="B32" t="n">
-        <v>82948</v>
+        <v>82975</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4135,50 +4135,45 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128314264</v>
+        <v>128315753</v>
       </c>
       <c r="B33" t="n">
-        <v>57689</v>
+        <v>91852</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>2062</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Getklövbäcken, Getklövbäcken, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>578451</v>
+        <v>578582</v>
       </c>
       <c r="R33" t="n">
-        <v>7053343</v>
+        <v>7053292</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4210,7 +4205,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>19:19</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4220,12 +4215,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>19:19</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4252,10 +4242,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128312941</v>
+        <v>128314264</v>
       </c>
       <c r="B34" t="n">
-        <v>79089</v>
+        <v>57716</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4263,34 +4253,39 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Getklövbäcken, Getklövbäcken, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>578353</v>
+        <v>578451</v>
       </c>
       <c r="R34" t="n">
-        <v>7053308</v>
+        <v>7053343</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4322,7 +4317,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>18:27</t>
+          <t>19:19</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4332,7 +4327,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>18:27</t>
+          <t>19:19</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4359,32 +4359,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128315753</v>
+        <v>128312941</v>
       </c>
       <c r="B35" t="n">
-        <v>91825</v>
+        <v>79116</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>2062</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4394,10 +4394,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>578582</v>
+        <v>578353</v>
       </c>
       <c r="R35" t="n">
-        <v>7053292</v>
+        <v>7053308</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4429,7 +4429,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>18:27</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4439,7 +4439,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>18:27</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4469,7 +4469,7 @@
         <v>128315601</v>
       </c>
       <c r="B36" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4586,7 +4586,7 @@
         <v>128314896</v>
       </c>
       <c r="B37" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4807,7 +4807,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128827795</v>
+        <v>128826746</v>
       </c>
       <c r="B39" t="n">
         <v>79116</v>
@@ -4842,10 +4842,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>578718</v>
+        <v>578626</v>
       </c>
       <c r="R39" t="n">
-        <v>7053164</v>
+        <v>7053261</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4877,7 +4877,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4887,7 +4887,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4914,7 +4914,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128826746</v>
+        <v>128827795</v>
       </c>
       <c r="B40" t="n">
         <v>79116</v>
@@ -4949,10 +4949,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>578626</v>
+        <v>578718</v>
       </c>
       <c r="R40" t="n">
-        <v>7053261</v>
+        <v>7053164</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4984,7 +4984,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4994,7 +4994,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5239,32 +5239,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128826443</v>
+        <v>128826236</v>
       </c>
       <c r="B43" t="n">
-        <v>96738</v>
+        <v>91494</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>2869</v>
+        <v>1202</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5274,10 +5274,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>578601</v>
+        <v>578567</v>
       </c>
       <c r="R43" t="n">
-        <v>7053281</v>
+        <v>7053297</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5309,7 +5309,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5319,7 +5319,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5346,32 +5346,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128826236</v>
+        <v>128826443</v>
       </c>
       <c r="B44" t="n">
-        <v>91494</v>
+        <v>96738</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1202</v>
+        <v>2869</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5381,10 +5381,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>578567</v>
+        <v>578601</v>
       </c>
       <c r="R44" t="n">
-        <v>7053297</v>
+        <v>7053281</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5416,7 +5416,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5426,7 +5426,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5677,45 +5677,49 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128828029</v>
+        <v>128827291</v>
       </c>
       <c r="B47" t="n">
-        <v>91790</v>
+        <v>98619</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Getklövbäcken, Getklövbäcken, Ång</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>578708</v>
+        <v>578691</v>
       </c>
       <c r="R47" t="n">
-        <v>7053135</v>
+        <v>7053218</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5747,7 +5751,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5757,7 +5761,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5784,49 +5788,45 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128827291</v>
+        <v>128828029</v>
       </c>
       <c r="B48" t="n">
-        <v>98619</v>
+        <v>91790</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Getklövbäcken, Getklövbäcken, Ång</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>578691</v>
+        <v>578708</v>
       </c>
       <c r="R48" t="n">
-        <v>7053218</v>
+        <v>7053135</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5858,7 +5858,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5868,7 +5868,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6332,10 +6332,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128827904</v>
+        <v>128826854</v>
       </c>
       <c r="B53" t="n">
-        <v>79116</v>
+        <v>82975</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6343,21 +6343,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6367,10 +6367,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>578704</v>
+        <v>578630</v>
       </c>
       <c r="R53" t="n">
-        <v>7053152</v>
+        <v>7053254</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6402,7 +6402,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6412,7 +6412,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6439,10 +6439,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128826854</v>
+        <v>128827904</v>
       </c>
       <c r="B54" t="n">
-        <v>82975</v>
+        <v>79116</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6450,21 +6450,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6474,10 +6474,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>578630</v>
+        <v>578704</v>
       </c>
       <c r="R54" t="n">
-        <v>7053254</v>
+        <v>7053152</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6509,7 +6509,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6519,7 +6519,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6653,10 +6653,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128830607</v>
+        <v>128827181</v>
       </c>
       <c r="B56" t="n">
-        <v>91512</v>
+        <v>57716</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6664,34 +6664,39 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Getklövbäcken, Getklövbäcken, Ång</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>578554</v>
+        <v>578677</v>
       </c>
       <c r="R56" t="n">
-        <v>7053252</v>
+        <v>7053213</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6723,7 +6728,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6733,7 +6738,12 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6867,10 +6877,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128827181</v>
+        <v>128830607</v>
       </c>
       <c r="B58" t="n">
-        <v>57716</v>
+        <v>91512</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6878,39 +6888,34 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Getklövbäcken, Getklövbäcken, Ång</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>578677</v>
+        <v>578554</v>
       </c>
       <c r="R58" t="n">
-        <v>7053213</v>
+        <v>7053252</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6942,7 +6947,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6952,12 +6957,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>16:01</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="AD58" t="b">

--- a/artfynd/A 44372-2024 artfynd.xlsx
+++ b/artfynd/A 44372-2024 artfynd.xlsx
@@ -3055,50 +3055,45 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128313900</v>
+        <v>128313672</v>
       </c>
       <c r="B23" t="n">
-        <v>57716</v>
+        <v>98640</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Getklövbäcken, Getklövbäcken, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>578364</v>
+        <v>578334</v>
       </c>
       <c r="R23" t="n">
-        <v>7053346</v>
+        <v>7053361</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3130,7 +3125,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>19:05</t>
+          <t>18:55</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3140,12 +3135,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>19:05</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>18:55</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3172,45 +3162,50 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128313672</v>
+        <v>128313900</v>
       </c>
       <c r="B24" t="n">
-        <v>98640</v>
+        <v>57716</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Getklövbäcken, Getklövbäcken, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>578334</v>
+        <v>578364</v>
       </c>
       <c r="R24" t="n">
-        <v>7053361</v>
+        <v>7053346</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3242,7 +3237,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>18:55</t>
+          <t>19:05</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3252,7 +3247,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>18:55</t>
+          <t>19:05</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -4703,7 +4703,7 @@
         <v>128828362</v>
       </c>
       <c r="B38" t="n">
-        <v>91695</v>
+        <v>91700</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4810,7 +4810,7 @@
         <v>128826746</v>
       </c>
       <c r="B39" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4917,7 +4917,7 @@
         <v>128827795</v>
       </c>
       <c r="B40" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5024,7 +5024,7 @@
         <v>128826730</v>
       </c>
       <c r="B41" t="n">
-        <v>92818</v>
+        <v>92823</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5132,32 +5132,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128827960</v>
+        <v>128826443</v>
       </c>
       <c r="B42" t="n">
-        <v>91494</v>
+        <v>96744</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1202</v>
+        <v>2869</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5167,10 +5167,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>578713</v>
+        <v>578601</v>
       </c>
       <c r="R42" t="n">
-        <v>7053139</v>
+        <v>7053281</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5202,7 +5202,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>16:39</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5212,7 +5212,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>16:39</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5239,10 +5239,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128826236</v>
+        <v>128827960</v>
       </c>
       <c r="B43" t="n">
-        <v>91494</v>
+        <v>91499</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5274,10 +5274,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>578567</v>
+        <v>578713</v>
       </c>
       <c r="R43" t="n">
-        <v>7053297</v>
+        <v>7053139</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5309,7 +5309,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>16:39</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5319,7 +5319,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>16:39</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5346,32 +5346,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128826443</v>
+        <v>128826236</v>
       </c>
       <c r="B44" t="n">
-        <v>96738</v>
+        <v>91499</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>2869</v>
+        <v>1202</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5381,10 +5381,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>578601</v>
+        <v>578567</v>
       </c>
       <c r="R44" t="n">
-        <v>7053281</v>
+        <v>7053297</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5416,7 +5416,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5426,7 +5426,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5456,7 +5456,7 @@
         <v>128827105</v>
       </c>
       <c r="B45" t="n">
-        <v>91494</v>
+        <v>91499</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5680,7 +5680,7 @@
         <v>128827291</v>
       </c>
       <c r="B47" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5791,7 +5791,7 @@
         <v>128828029</v>
       </c>
       <c r="B48" t="n">
-        <v>91790</v>
+        <v>91795</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5898,7 +5898,7 @@
         <v>128827406</v>
       </c>
       <c r="B49" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6005,7 +6005,7 @@
         <v>128828721</v>
       </c>
       <c r="B50" t="n">
-        <v>96738</v>
+        <v>96744</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6112,7 +6112,7 @@
         <v>128827329</v>
       </c>
       <c r="B51" t="n">
-        <v>82975</v>
+        <v>82979</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6335,7 +6335,7 @@
         <v>128826854</v>
       </c>
       <c r="B53" t="n">
-        <v>82975</v>
+        <v>82979</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6442,7 +6442,7 @@
         <v>128827904</v>
       </c>
       <c r="B54" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6549,7 +6549,7 @@
         <v>128830025</v>
       </c>
       <c r="B55" t="n">
-        <v>91512</v>
+        <v>91517</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6653,10 +6653,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128827181</v>
+        <v>128827117</v>
       </c>
       <c r="B56" t="n">
-        <v>57716</v>
+        <v>79120</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6664,39 +6664,34 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Getklövbäcken, Getklövbäcken, Ång</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>578677</v>
+        <v>578673</v>
       </c>
       <c r="R56" t="n">
-        <v>7053213</v>
+        <v>7053215</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6728,7 +6723,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6738,12 +6733,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>16:01</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6770,10 +6760,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128827117</v>
+        <v>128827181</v>
       </c>
       <c r="B57" t="n">
-        <v>79116</v>
+        <v>57716</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6781,34 +6771,39 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Getklövbäcken, Getklövbäcken, Ång</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>578673</v>
+        <v>578677</v>
       </c>
       <c r="R57" t="n">
-        <v>7053215</v>
+        <v>7053213</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6840,7 +6835,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6850,7 +6845,12 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6880,7 +6880,7 @@
         <v>128830607</v>
       </c>
       <c r="B58" t="n">
-        <v>91512</v>
+        <v>91517</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6987,7 +6987,7 @@
         <v>128827078</v>
       </c>
       <c r="B59" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7094,7 +7094,7 @@
         <v>128826680</v>
       </c>
       <c r="B60" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7201,7 +7201,7 @@
         <v>128828903</v>
       </c>
       <c r="B61" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7308,7 +7308,7 @@
         <v>128829015</v>
       </c>
       <c r="B62" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>

--- a/artfynd/A 44372-2024 artfynd.xlsx
+++ b/artfynd/A 44372-2024 artfynd.xlsx
@@ -2630,7 +2630,7 @@
         <v>128313607</v>
       </c>
       <c r="B19" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2737,7 +2737,7 @@
         <v>128314993</v>
       </c>
       <c r="B20" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2844,7 +2844,7 @@
         <v>128315431</v>
       </c>
       <c r="B21" t="n">
-        <v>91512</v>
+        <v>91522</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2951,7 +2951,7 @@
         <v>128315158</v>
       </c>
       <c r="B22" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3055,45 +3055,50 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128313672</v>
+        <v>128313900</v>
       </c>
       <c r="B23" t="n">
-        <v>98640</v>
+        <v>57716</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Getklövbäcken, Getklövbäcken, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>578334</v>
+        <v>578364</v>
       </c>
       <c r="R23" t="n">
-        <v>7053361</v>
+        <v>7053346</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3125,7 +3130,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>18:55</t>
+          <t>19:05</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3135,7 +3140,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>18:55</t>
+          <t>19:05</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3162,50 +3172,45 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128313900</v>
+        <v>128313672</v>
       </c>
       <c r="B24" t="n">
-        <v>57716</v>
+        <v>98653</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Getklövbäcken, Getklövbäcken, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>578364</v>
+        <v>578334</v>
       </c>
       <c r="R24" t="n">
-        <v>7053346</v>
+        <v>7053361</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3237,7 +3242,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>19:05</t>
+          <t>18:55</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3247,12 +3252,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>19:05</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>18:55</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3282,7 +3282,7 @@
         <v>128313998</v>
       </c>
       <c r="B25" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3389,7 +3389,7 @@
         <v>128312862</v>
       </c>
       <c r="B26" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3493,10 +3493,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128313227</v>
+        <v>128315722</v>
       </c>
       <c r="B27" t="n">
-        <v>79116</v>
+        <v>91504</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3504,21 +3504,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3528,10 +3528,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>578343</v>
+        <v>578585</v>
       </c>
       <c r="R27" t="n">
-        <v>7053335</v>
+        <v>7053294</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3563,7 +3563,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>18:37</t>
+          <t>20:18</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3573,7 +3573,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>18:37</t>
+          <t>20:18</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3600,10 +3600,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128315722</v>
+        <v>128313227</v>
       </c>
       <c r="B28" t="n">
-        <v>91494</v>
+        <v>79120</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3611,21 +3611,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3635,10 +3635,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>578585</v>
+        <v>578343</v>
       </c>
       <c r="R28" t="n">
-        <v>7053294</v>
+        <v>7053335</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3670,7 +3670,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>20:18</t>
+          <t>18:37</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3680,7 +3680,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>20:18</t>
+          <t>18:37</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3710,7 +3710,7 @@
         <v>128315521</v>
       </c>
       <c r="B29" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3817,7 +3817,7 @@
         <v>128313403</v>
       </c>
       <c r="B30" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3924,7 +3924,7 @@
         <v>128313653</v>
       </c>
       <c r="B31" t="n">
-        <v>96738</v>
+        <v>96751</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4031,7 +4031,7 @@
         <v>128313502</v>
       </c>
       <c r="B32" t="n">
-        <v>82975</v>
+        <v>82979</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4138,7 +4138,7 @@
         <v>128315753</v>
       </c>
       <c r="B33" t="n">
-        <v>91852</v>
+        <v>91862</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4242,10 +4242,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128314264</v>
+        <v>128312941</v>
       </c>
       <c r="B34" t="n">
-        <v>57716</v>
+        <v>79120</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4253,39 +4253,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Getklövbäcken, Getklövbäcken, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>578451</v>
+        <v>578353</v>
       </c>
       <c r="R34" t="n">
-        <v>7053343</v>
+        <v>7053308</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4317,7 +4312,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>19:19</t>
+          <t>18:27</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4327,12 +4322,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>19:19</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>18:27</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4359,10 +4349,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128312941</v>
+        <v>128314264</v>
       </c>
       <c r="B35" t="n">
-        <v>79116</v>
+        <v>57716</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4370,34 +4360,39 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Getklövbäcken, Getklövbäcken, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>578353</v>
+        <v>578451</v>
       </c>
       <c r="R35" t="n">
-        <v>7053308</v>
+        <v>7053343</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4429,7 +4424,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>18:27</t>
+          <t>19:19</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4439,7 +4434,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>18:27</t>
+          <t>19:19</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4703,7 +4703,7 @@
         <v>128828362</v>
       </c>
       <c r="B38" t="n">
-        <v>91700</v>
+        <v>91705</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5024,7 +5024,7 @@
         <v>128826730</v>
       </c>
       <c r="B41" t="n">
-        <v>92823</v>
+        <v>92830</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5132,32 +5132,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128826443</v>
+        <v>128827960</v>
       </c>
       <c r="B42" t="n">
-        <v>96744</v>
+        <v>91504</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>2869</v>
+        <v>1202</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5167,10 +5167,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>578601</v>
+        <v>578713</v>
       </c>
       <c r="R42" t="n">
-        <v>7053281</v>
+        <v>7053139</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5202,7 +5202,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>16:39</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5212,7 +5212,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>16:39</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5239,10 +5239,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128827960</v>
+        <v>128826236</v>
       </c>
       <c r="B43" t="n">
-        <v>91499</v>
+        <v>91504</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5274,10 +5274,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>578713</v>
+        <v>578567</v>
       </c>
       <c r="R43" t="n">
-        <v>7053139</v>
+        <v>7053297</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5309,7 +5309,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>16:39</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5319,7 +5319,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>16:39</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5346,32 +5346,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128826236</v>
+        <v>128826443</v>
       </c>
       <c r="B44" t="n">
-        <v>91499</v>
+        <v>96751</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1202</v>
+        <v>2869</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5381,10 +5381,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>578567</v>
+        <v>578601</v>
       </c>
       <c r="R44" t="n">
-        <v>7053297</v>
+        <v>7053281</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5416,7 +5416,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5426,7 +5426,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5456,7 +5456,7 @@
         <v>128827105</v>
       </c>
       <c r="B45" t="n">
-        <v>91499</v>
+        <v>91504</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5677,49 +5677,45 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128827291</v>
+        <v>128828029</v>
       </c>
       <c r="B47" t="n">
-        <v>98625</v>
+        <v>91800</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Getklövbäcken, Getklövbäcken, Ång</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>578691</v>
+        <v>578708</v>
       </c>
       <c r="R47" t="n">
-        <v>7053218</v>
+        <v>7053135</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5751,7 +5747,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5761,7 +5757,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5788,45 +5784,49 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128828029</v>
+        <v>128827291</v>
       </c>
       <c r="B48" t="n">
-        <v>91795</v>
+        <v>98632</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Getklövbäcken, Getklövbäcken, Ång</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>578708</v>
+        <v>578691</v>
       </c>
       <c r="R48" t="n">
-        <v>7053135</v>
+        <v>7053218</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5858,7 +5858,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5868,7 +5868,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6005,7 +6005,7 @@
         <v>128828721</v>
       </c>
       <c r="B50" t="n">
-        <v>96744</v>
+        <v>96751</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6549,7 +6549,7 @@
         <v>128830025</v>
       </c>
       <c r="B55" t="n">
-        <v>91517</v>
+        <v>91522</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6760,10 +6760,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128827181</v>
+        <v>128830607</v>
       </c>
       <c r="B57" t="n">
-        <v>57716</v>
+        <v>91522</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6771,39 +6771,34 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Getklövbäcken, Getklövbäcken, Ång</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>578677</v>
+        <v>578554</v>
       </c>
       <c r="R57" t="n">
-        <v>7053213</v>
+        <v>7053252</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6835,7 +6830,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6845,12 +6840,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>16:01</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6877,10 +6867,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128830607</v>
+        <v>128827181</v>
       </c>
       <c r="B58" t="n">
-        <v>91517</v>
+        <v>57716</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6888,34 +6878,39 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Getklövbäcken, Getklövbäcken, Ång</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>578554</v>
+        <v>578677</v>
       </c>
       <c r="R58" t="n">
-        <v>7053252</v>
+        <v>7053213</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6947,7 +6942,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6957,7 +6952,12 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7308,7 +7308,7 @@
         <v>128829015</v>
       </c>
       <c r="B62" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>

--- a/artfynd/A 44372-2024 artfynd.xlsx
+++ b/artfynd/A 44372-2024 artfynd.xlsx
@@ -3493,10 +3493,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128315722</v>
+        <v>128313227</v>
       </c>
       <c r="B27" t="n">
-        <v>91504</v>
+        <v>79120</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3504,21 +3504,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3528,10 +3528,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>578585</v>
+        <v>578343</v>
       </c>
       <c r="R27" t="n">
-        <v>7053294</v>
+        <v>7053335</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3563,7 +3563,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>20:18</t>
+          <t>18:37</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3573,7 +3573,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>20:18</t>
+          <t>18:37</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3600,10 +3600,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128313227</v>
+        <v>128315722</v>
       </c>
       <c r="B28" t="n">
-        <v>79120</v>
+        <v>91504</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3611,21 +3611,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3635,10 +3635,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>578343</v>
+        <v>578585</v>
       </c>
       <c r="R28" t="n">
-        <v>7053335</v>
+        <v>7053294</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3670,7 +3670,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>18:37</t>
+          <t>20:18</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3680,7 +3680,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>18:37</t>
+          <t>20:18</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4028,10 +4028,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128313502</v>
+        <v>128314264</v>
       </c>
       <c r="B32" t="n">
-        <v>82979</v>
+        <v>57716</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4039,31 +4039,36 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Getklövbäcken, Getklövbäcken, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>578334</v>
+        <v>578451</v>
       </c>
       <c r="R32" t="n">
         <v>7053343</v>
@@ -4098,7 +4103,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>18:47</t>
+          <t>19:19</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4108,7 +4113,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>18:47</t>
+          <t>19:19</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4135,32 +4145,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128315753</v>
+        <v>128312941</v>
       </c>
       <c r="B33" t="n">
-        <v>91862</v>
+        <v>79120</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>2062</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4170,10 +4180,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>578582</v>
+        <v>578353</v>
       </c>
       <c r="R33" t="n">
-        <v>7053292</v>
+        <v>7053308</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4205,7 +4215,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>18:27</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4215,7 +4225,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>18:27</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4242,10 +4252,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128312941</v>
+        <v>128313502</v>
       </c>
       <c r="B34" t="n">
-        <v>79120</v>
+        <v>82979</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4253,21 +4263,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4277,10 +4287,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>578353</v>
+        <v>578334</v>
       </c>
       <c r="R34" t="n">
-        <v>7053308</v>
+        <v>7053343</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4312,7 +4322,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>18:27</t>
+          <t>18:47</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4322,7 +4332,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>18:27</t>
+          <t>18:47</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4349,50 +4359,45 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128314264</v>
+        <v>128315753</v>
       </c>
       <c r="B35" t="n">
-        <v>57716</v>
+        <v>91862</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>2062</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Getklövbäcken, Getklövbäcken, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>578451</v>
+        <v>578582</v>
       </c>
       <c r="R35" t="n">
-        <v>7053343</v>
+        <v>7053292</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4424,7 +4429,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>19:19</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4434,12 +4439,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>19:19</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -6332,10 +6332,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128826854</v>
+        <v>128827904</v>
       </c>
       <c r="B53" t="n">
-        <v>82979</v>
+        <v>79120</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6343,21 +6343,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6367,10 +6367,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>578630</v>
+        <v>578704</v>
       </c>
       <c r="R53" t="n">
-        <v>7053254</v>
+        <v>7053152</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6402,7 +6402,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6412,7 +6412,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6439,10 +6439,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128827904</v>
+        <v>128826854</v>
       </c>
       <c r="B54" t="n">
-        <v>79120</v>
+        <v>82979</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6450,21 +6450,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6474,10 +6474,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>578704</v>
+        <v>578630</v>
       </c>
       <c r="R54" t="n">
-        <v>7053152</v>
+        <v>7053254</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6509,7 +6509,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6519,7 +6519,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6653,10 +6653,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128827117</v>
+        <v>128830607</v>
       </c>
       <c r="B56" t="n">
-        <v>79120</v>
+        <v>91522</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6664,21 +6664,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6688,10 +6688,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>578673</v>
+        <v>578554</v>
       </c>
       <c r="R56" t="n">
-        <v>7053215</v>
+        <v>7053252</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6723,7 +6723,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6733,7 +6733,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6760,10 +6760,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128830607</v>
+        <v>128827117</v>
       </c>
       <c r="B57" t="n">
-        <v>91522</v>
+        <v>79120</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6771,21 +6771,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6795,10 +6795,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>578554</v>
+        <v>578673</v>
       </c>
       <c r="R57" t="n">
-        <v>7053252</v>
+        <v>7053215</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6830,7 +6830,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6840,7 +6840,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AD57" t="b">

--- a/artfynd/A 44372-2024 artfynd.xlsx
+++ b/artfynd/A 44372-2024 artfynd.xlsx
@@ -5132,32 +5132,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128827960</v>
+        <v>128826443</v>
       </c>
       <c r="B42" t="n">
-        <v>91504</v>
+        <v>96751</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1202</v>
+        <v>2869</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5167,10 +5167,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>578713</v>
+        <v>578601</v>
       </c>
       <c r="R42" t="n">
-        <v>7053139</v>
+        <v>7053281</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5202,7 +5202,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>16:39</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5212,7 +5212,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>16:39</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5239,7 +5239,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128826236</v>
+        <v>128827960</v>
       </c>
       <c r="B43" t="n">
         <v>91504</v>
@@ -5274,10 +5274,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>578567</v>
+        <v>578713</v>
       </c>
       <c r="R43" t="n">
-        <v>7053297</v>
+        <v>7053139</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5309,7 +5309,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>16:39</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5319,7 +5319,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>16:39</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5346,32 +5346,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128826443</v>
+        <v>128826236</v>
       </c>
       <c r="B44" t="n">
-        <v>96751</v>
+        <v>91504</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>2869</v>
+        <v>1202</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5381,10 +5381,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>578601</v>
+        <v>578567</v>
       </c>
       <c r="R44" t="n">
-        <v>7053281</v>
+        <v>7053297</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5416,7 +5416,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5426,7 +5426,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -6332,10 +6332,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128827904</v>
+        <v>128826854</v>
       </c>
       <c r="B53" t="n">
-        <v>79120</v>
+        <v>82979</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6343,21 +6343,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6367,10 +6367,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>578704</v>
+        <v>578630</v>
       </c>
       <c r="R53" t="n">
-        <v>7053152</v>
+        <v>7053254</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6402,7 +6402,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6412,7 +6412,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6439,10 +6439,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128826854</v>
+        <v>128827904</v>
       </c>
       <c r="B54" t="n">
-        <v>82979</v>
+        <v>79120</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6450,21 +6450,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6474,10 +6474,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>578630</v>
+        <v>578704</v>
       </c>
       <c r="R54" t="n">
-        <v>7053254</v>
+        <v>7053152</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6509,7 +6509,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6519,7 +6519,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6760,10 +6760,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128827117</v>
+        <v>128827181</v>
       </c>
       <c r="B57" t="n">
-        <v>79120</v>
+        <v>57716</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6771,34 +6771,39 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Getklövbäcken, Getklövbäcken, Ång</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>578673</v>
+        <v>578677</v>
       </c>
       <c r="R57" t="n">
-        <v>7053215</v>
+        <v>7053213</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6830,7 +6835,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6840,7 +6845,12 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6867,10 +6877,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128827181</v>
+        <v>128827117</v>
       </c>
       <c r="B58" t="n">
-        <v>57716</v>
+        <v>79120</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6878,39 +6888,34 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Getklövbäcken, Getklövbäcken, Ång</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>578677</v>
+        <v>578673</v>
       </c>
       <c r="R58" t="n">
-        <v>7053213</v>
+        <v>7053215</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6942,7 +6947,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6952,12 +6957,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>16:01</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AD58" t="b">

--- a/artfynd/A 44372-2024 artfynd.xlsx
+++ b/artfynd/A 44372-2024 artfynd.xlsx
@@ -3493,10 +3493,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128313227</v>
+        <v>128315722</v>
       </c>
       <c r="B27" t="n">
-        <v>79120</v>
+        <v>91504</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3504,21 +3504,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3528,10 +3528,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>578343</v>
+        <v>578585</v>
       </c>
       <c r="R27" t="n">
-        <v>7053335</v>
+        <v>7053294</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3563,7 +3563,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>18:37</t>
+          <t>20:18</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3573,7 +3573,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>18:37</t>
+          <t>20:18</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3600,10 +3600,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128315722</v>
+        <v>128313227</v>
       </c>
       <c r="B28" t="n">
-        <v>91504</v>
+        <v>79120</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3611,21 +3611,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3635,10 +3635,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>578585</v>
+        <v>578343</v>
       </c>
       <c r="R28" t="n">
-        <v>7053294</v>
+        <v>7053335</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3670,7 +3670,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>20:18</t>
+          <t>18:37</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3680,7 +3680,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>20:18</t>
+          <t>18:37</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3707,7 +3707,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128315521</v>
+        <v>128313403</v>
       </c>
       <c r="B29" t="n">
         <v>79120</v>
@@ -3742,10 +3742,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>578575</v>
+        <v>578327</v>
       </c>
       <c r="R29" t="n">
-        <v>7053303</v>
+        <v>7053341</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3777,7 +3777,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>20:07</t>
+          <t>18:43</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3787,7 +3787,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>20:07</t>
+          <t>18:43</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3814,7 +3814,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128313403</v>
+        <v>128315521</v>
       </c>
       <c r="B30" t="n">
         <v>79120</v>
@@ -3849,10 +3849,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>578327</v>
+        <v>578575</v>
       </c>
       <c r="R30" t="n">
-        <v>7053341</v>
+        <v>7053303</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3884,7 +3884,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>18:43</t>
+          <t>20:07</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3894,7 +3894,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>18:43</t>
+          <t>20:07</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4028,50 +4028,45 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128314264</v>
+        <v>128315753</v>
       </c>
       <c r="B32" t="n">
-        <v>57716</v>
+        <v>91862</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>2062</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Getklövbäcken, Getklövbäcken, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>578451</v>
+        <v>578582</v>
       </c>
       <c r="R32" t="n">
-        <v>7053343</v>
+        <v>7053292</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4103,7 +4098,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>19:19</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4113,12 +4108,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>19:19</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4145,10 +4135,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128312941</v>
+        <v>128313502</v>
       </c>
       <c r="B33" t="n">
-        <v>79120</v>
+        <v>82979</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4156,21 +4146,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4180,10 +4170,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>578353</v>
+        <v>578334</v>
       </c>
       <c r="R33" t="n">
-        <v>7053308</v>
+        <v>7053343</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4215,7 +4205,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>18:27</t>
+          <t>18:47</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4225,7 +4215,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>18:27</t>
+          <t>18:47</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4252,10 +4242,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128313502</v>
+        <v>128312941</v>
       </c>
       <c r="B34" t="n">
-        <v>82979</v>
+        <v>79120</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4263,21 +4253,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4287,10 +4277,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>578334</v>
+        <v>578353</v>
       </c>
       <c r="R34" t="n">
-        <v>7053343</v>
+        <v>7053308</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4322,7 +4312,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>18:47</t>
+          <t>18:27</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4332,7 +4322,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>18:47</t>
+          <t>18:27</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4359,45 +4349,50 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128315753</v>
+        <v>128314264</v>
       </c>
       <c r="B35" t="n">
-        <v>91862</v>
+        <v>57716</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>2062</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Getklövbäcken, Getklövbäcken, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>578582</v>
+        <v>578451</v>
       </c>
       <c r="R35" t="n">
-        <v>7053292</v>
+        <v>7053343</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4429,7 +4424,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>19:19</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4439,7 +4434,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>19:19</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4703,7 +4703,7 @@
         <v>128828362</v>
       </c>
       <c r="B38" t="n">
-        <v>91705</v>
+        <v>91709</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4810,7 +4810,7 @@
         <v>128826746</v>
       </c>
       <c r="B39" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4917,7 +4917,7 @@
         <v>128827795</v>
       </c>
       <c r="B40" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5024,7 +5024,7 @@
         <v>128826730</v>
       </c>
       <c r="B41" t="n">
-        <v>92830</v>
+        <v>92834</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5135,7 +5135,7 @@
         <v>128826443</v>
       </c>
       <c r="B42" t="n">
-        <v>96751</v>
+        <v>96755</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5242,7 +5242,7 @@
         <v>128827960</v>
       </c>
       <c r="B43" t="n">
-        <v>91504</v>
+        <v>91508</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5349,7 +5349,7 @@
         <v>128826236</v>
       </c>
       <c r="B44" t="n">
-        <v>91504</v>
+        <v>91508</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5456,7 +5456,7 @@
         <v>128827105</v>
       </c>
       <c r="B45" t="n">
-        <v>91504</v>
+        <v>91508</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5563,7 +5563,7 @@
         <v>128828240</v>
       </c>
       <c r="B46" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5680,7 +5680,7 @@
         <v>128828029</v>
       </c>
       <c r="B47" t="n">
-        <v>91800</v>
+        <v>91804</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5787,7 +5787,7 @@
         <v>128827291</v>
       </c>
       <c r="B48" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5898,7 +5898,7 @@
         <v>128827406</v>
       </c>
       <c r="B49" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6005,7 +6005,7 @@
         <v>128828721</v>
       </c>
       <c r="B50" t="n">
-        <v>96751</v>
+        <v>96755</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6112,7 +6112,7 @@
         <v>128827329</v>
       </c>
       <c r="B51" t="n">
-        <v>82979</v>
+        <v>82983</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6219,7 +6219,7 @@
         <v>128826703</v>
       </c>
       <c r="B52" t="n">
-        <v>57876</v>
+        <v>57880</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6335,7 +6335,7 @@
         <v>128826854</v>
       </c>
       <c r="B53" t="n">
-        <v>82979</v>
+        <v>82983</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6442,7 +6442,7 @@
         <v>128827904</v>
       </c>
       <c r="B54" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6549,7 +6549,7 @@
         <v>128830025</v>
       </c>
       <c r="B55" t="n">
-        <v>91522</v>
+        <v>91526</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6656,7 +6656,7 @@
         <v>128830607</v>
       </c>
       <c r="B56" t="n">
-        <v>91522</v>
+        <v>91526</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6760,10 +6760,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128827181</v>
+        <v>128827117</v>
       </c>
       <c r="B57" t="n">
-        <v>57716</v>
+        <v>79124</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6771,39 +6771,34 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Getklövbäcken, Getklövbäcken, Ång</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>578677</v>
+        <v>578673</v>
       </c>
       <c r="R57" t="n">
-        <v>7053213</v>
+        <v>7053215</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6835,7 +6830,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6845,12 +6840,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>16:01</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6877,10 +6867,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128827117</v>
+        <v>128827181</v>
       </c>
       <c r="B58" t="n">
-        <v>79120</v>
+        <v>57720</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6888,34 +6878,39 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Getklövbäcken, Getklövbäcken, Ång</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>578673</v>
+        <v>578677</v>
       </c>
       <c r="R58" t="n">
-        <v>7053215</v>
+        <v>7053213</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6947,7 +6942,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6957,7 +6952,12 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6987,7 +6987,7 @@
         <v>128827078</v>
       </c>
       <c r="B59" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7094,7 +7094,7 @@
         <v>128826680</v>
       </c>
       <c r="B60" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7201,7 +7201,7 @@
         <v>128828903</v>
       </c>
       <c r="B61" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7308,7 +7308,7 @@
         <v>128829015</v>
       </c>
       <c r="B62" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>

--- a/artfynd/A 44372-2024 artfynd.xlsx
+++ b/artfynd/A 44372-2024 artfynd.xlsx
@@ -5132,32 +5132,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128826443</v>
+        <v>128827960</v>
       </c>
       <c r="B42" t="n">
-        <v>96755</v>
+        <v>91508</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>2869</v>
+        <v>1202</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5167,10 +5167,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>578601</v>
+        <v>578713</v>
       </c>
       <c r="R42" t="n">
-        <v>7053281</v>
+        <v>7053139</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5202,7 +5202,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>16:39</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5212,7 +5212,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>16:39</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5239,7 +5239,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128827960</v>
+        <v>128826236</v>
       </c>
       <c r="B43" t="n">
         <v>91508</v>
@@ -5274,10 +5274,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>578713</v>
+        <v>578567</v>
       </c>
       <c r="R43" t="n">
-        <v>7053139</v>
+        <v>7053297</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5309,7 +5309,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>16:39</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5319,7 +5319,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>16:39</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5346,32 +5346,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128826236</v>
+        <v>128826443</v>
       </c>
       <c r="B44" t="n">
-        <v>91508</v>
+        <v>96755</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1202</v>
+        <v>2869</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5381,10 +5381,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>578567</v>
+        <v>578601</v>
       </c>
       <c r="R44" t="n">
-        <v>7053297</v>
+        <v>7053281</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5416,7 +5416,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5426,7 +5426,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -6332,10 +6332,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128826854</v>
+        <v>128827904</v>
       </c>
       <c r="B53" t="n">
-        <v>82983</v>
+        <v>79124</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6343,21 +6343,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6367,10 +6367,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>578630</v>
+        <v>578704</v>
       </c>
       <c r="R53" t="n">
-        <v>7053254</v>
+        <v>7053152</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6402,7 +6402,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6412,7 +6412,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6439,10 +6439,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128827904</v>
+        <v>128826854</v>
       </c>
       <c r="B54" t="n">
-        <v>79124</v>
+        <v>82983</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6450,21 +6450,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6474,10 +6474,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>578704</v>
+        <v>578630</v>
       </c>
       <c r="R54" t="n">
-        <v>7053152</v>
+        <v>7053254</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6509,7 +6509,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6519,7 +6519,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6653,10 +6653,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128830607</v>
+        <v>128827181</v>
       </c>
       <c r="B56" t="n">
-        <v>91526</v>
+        <v>57720</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6664,34 +6664,39 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Getklövbäcken, Getklövbäcken, Ång</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>578554</v>
+        <v>578677</v>
       </c>
       <c r="R56" t="n">
-        <v>7053252</v>
+        <v>7053213</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6723,7 +6728,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6733,7 +6738,12 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6760,10 +6770,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128827117</v>
+        <v>128830607</v>
       </c>
       <c r="B57" t="n">
-        <v>79124</v>
+        <v>91526</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6771,21 +6781,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6795,10 +6805,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>578673</v>
+        <v>578554</v>
       </c>
       <c r="R57" t="n">
-        <v>7053215</v>
+        <v>7053252</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6830,7 +6840,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6840,7 +6850,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6867,10 +6877,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128827181</v>
+        <v>128827117</v>
       </c>
       <c r="B58" t="n">
-        <v>57720</v>
+        <v>79124</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6878,39 +6888,34 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Getklövbäcken, Getklövbäcken, Ång</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>578677</v>
+        <v>578673</v>
       </c>
       <c r="R58" t="n">
-        <v>7053213</v>
+        <v>7053215</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6942,7 +6947,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6952,12 +6957,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>16:01</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AD58" t="b">

--- a/artfynd/A 44372-2024 artfynd.xlsx
+++ b/artfynd/A 44372-2024 artfynd.xlsx
@@ -4703,7 +4703,7 @@
         <v>128828362</v>
       </c>
       <c r="B38" t="n">
-        <v>91709</v>
+        <v>91714</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4810,7 +4810,7 @@
         <v>128826746</v>
       </c>
       <c r="B39" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4917,7 +4917,7 @@
         <v>128827795</v>
       </c>
       <c r="B40" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5024,7 +5024,7 @@
         <v>128826730</v>
       </c>
       <c r="B41" t="n">
-        <v>92834</v>
+        <v>92839</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5132,32 +5132,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128827960</v>
+        <v>128826443</v>
       </c>
       <c r="B42" t="n">
-        <v>91508</v>
+        <v>96762</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1202</v>
+        <v>2869</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5167,10 +5167,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>578713</v>
+        <v>578601</v>
       </c>
       <c r="R42" t="n">
-        <v>7053139</v>
+        <v>7053281</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5202,7 +5202,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>16:39</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5212,7 +5212,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>16:39</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5239,10 +5239,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128826236</v>
+        <v>128827960</v>
       </c>
       <c r="B43" t="n">
-        <v>91508</v>
+        <v>91513</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5274,10 +5274,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>578567</v>
+        <v>578713</v>
       </c>
       <c r="R43" t="n">
-        <v>7053297</v>
+        <v>7053139</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5309,7 +5309,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>16:39</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5319,7 +5319,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>16:39</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5346,32 +5346,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128826443</v>
+        <v>128826236</v>
       </c>
       <c r="B44" t="n">
-        <v>96755</v>
+        <v>91513</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>2869</v>
+        <v>1202</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5381,10 +5381,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>578601</v>
+        <v>578567</v>
       </c>
       <c r="R44" t="n">
-        <v>7053281</v>
+        <v>7053297</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5416,7 +5416,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5426,7 +5426,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5456,7 +5456,7 @@
         <v>128827105</v>
       </c>
       <c r="B45" t="n">
-        <v>91508</v>
+        <v>91513</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5563,7 +5563,7 @@
         <v>128828240</v>
       </c>
       <c r="B46" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5680,7 +5680,7 @@
         <v>128828029</v>
       </c>
       <c r="B47" t="n">
-        <v>91804</v>
+        <v>91809</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5787,7 +5787,7 @@
         <v>128827291</v>
       </c>
       <c r="B48" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5898,7 +5898,7 @@
         <v>128827406</v>
       </c>
       <c r="B49" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6005,7 +6005,7 @@
         <v>128828721</v>
       </c>
       <c r="B50" t="n">
-        <v>96755</v>
+        <v>96762</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6112,7 +6112,7 @@
         <v>128827329</v>
       </c>
       <c r="B51" t="n">
-        <v>82983</v>
+        <v>82892</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6219,7 +6219,7 @@
         <v>128826703</v>
       </c>
       <c r="B52" t="n">
-        <v>57880</v>
+        <v>57883</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6332,10 +6332,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128827904</v>
+        <v>128826854</v>
       </c>
       <c r="B53" t="n">
-        <v>79124</v>
+        <v>82892</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6343,21 +6343,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6367,10 +6367,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>578704</v>
+        <v>578630</v>
       </c>
       <c r="R53" t="n">
-        <v>7053152</v>
+        <v>7053254</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6402,7 +6402,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6412,7 +6412,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6439,10 +6439,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128826854</v>
+        <v>128827904</v>
       </c>
       <c r="B54" t="n">
-        <v>82983</v>
+        <v>79029</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6450,21 +6450,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6474,10 +6474,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>578630</v>
+        <v>578704</v>
       </c>
       <c r="R54" t="n">
-        <v>7053254</v>
+        <v>7053152</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6509,7 +6509,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6519,7 +6519,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6549,7 +6549,7 @@
         <v>128830025</v>
       </c>
       <c r="B55" t="n">
-        <v>91526</v>
+        <v>91531</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6653,10 +6653,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128827181</v>
+        <v>128830607</v>
       </c>
       <c r="B56" t="n">
-        <v>57720</v>
+        <v>91531</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6664,39 +6664,34 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Getklövbäcken, Getklövbäcken, Ång</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>578677</v>
+        <v>578554</v>
       </c>
       <c r="R56" t="n">
-        <v>7053213</v>
+        <v>7053252</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6728,7 +6723,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6738,12 +6733,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>16:01</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6770,10 +6760,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128830607</v>
+        <v>128827117</v>
       </c>
       <c r="B57" t="n">
-        <v>91526</v>
+        <v>79029</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6781,21 +6771,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6805,10 +6795,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>578554</v>
+        <v>578673</v>
       </c>
       <c r="R57" t="n">
-        <v>7053252</v>
+        <v>7053215</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6840,7 +6830,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6850,7 +6840,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6877,10 +6867,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128827117</v>
+        <v>128827181</v>
       </c>
       <c r="B58" t="n">
-        <v>79124</v>
+        <v>57723</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6888,34 +6878,39 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Getklövbäcken, Getklövbäcken, Ång</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>578673</v>
+        <v>578677</v>
       </c>
       <c r="R58" t="n">
-        <v>7053215</v>
+        <v>7053213</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6947,7 +6942,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6957,7 +6952,12 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6987,7 +6987,7 @@
         <v>128827078</v>
       </c>
       <c r="B59" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7094,7 +7094,7 @@
         <v>128826680</v>
       </c>
       <c r="B60" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7201,7 +7201,7 @@
         <v>128828903</v>
       </c>
       <c r="B61" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7308,7 +7308,7 @@
         <v>128829015</v>
       </c>
       <c r="B62" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>

--- a/artfynd/A 44372-2024 artfynd.xlsx
+++ b/artfynd/A 44372-2024 artfynd.xlsx
@@ -5132,32 +5132,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128826443</v>
+        <v>128827960</v>
       </c>
       <c r="B42" t="n">
-        <v>96770</v>
+        <v>91520</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>2869</v>
+        <v>1202</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5167,10 +5167,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>578601</v>
+        <v>578713</v>
       </c>
       <c r="R42" t="n">
-        <v>7053281</v>
+        <v>7053139</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5202,7 +5202,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>16:39</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5212,7 +5212,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>16:39</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5239,7 +5239,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128827960</v>
+        <v>128826236</v>
       </c>
       <c r="B43" t="n">
         <v>91520</v>
@@ -5274,10 +5274,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>578713</v>
+        <v>578567</v>
       </c>
       <c r="R43" t="n">
-        <v>7053139</v>
+        <v>7053297</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5309,7 +5309,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>16:39</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5319,7 +5319,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>16:39</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5346,32 +5346,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128826236</v>
+        <v>128826443</v>
       </c>
       <c r="B44" t="n">
-        <v>91520</v>
+        <v>96770</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1202</v>
+        <v>2869</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5381,10 +5381,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>578567</v>
+        <v>578601</v>
       </c>
       <c r="R44" t="n">
-        <v>7053297</v>
+        <v>7053281</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5416,7 +5416,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5426,7 +5426,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -6332,10 +6332,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128827904</v>
+        <v>128826854</v>
       </c>
       <c r="B53" t="n">
-        <v>79034</v>
+        <v>82897</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6343,21 +6343,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6367,10 +6367,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>578704</v>
+        <v>578630</v>
       </c>
       <c r="R53" t="n">
-        <v>7053152</v>
+        <v>7053254</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6402,7 +6402,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6412,7 +6412,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6439,10 +6439,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128826854</v>
+        <v>128827904</v>
       </c>
       <c r="B54" t="n">
-        <v>82897</v>
+        <v>79034</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6450,21 +6450,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6474,10 +6474,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>578630</v>
+        <v>578704</v>
       </c>
       <c r="R54" t="n">
-        <v>7053254</v>
+        <v>7053152</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6509,7 +6509,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6519,7 +6519,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6653,10 +6653,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128830607</v>
+        <v>128827181</v>
       </c>
       <c r="B56" t="n">
-        <v>91538</v>
+        <v>57723</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6664,34 +6664,39 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Getklövbäcken, Getklövbäcken, Ång</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>578554</v>
+        <v>578677</v>
       </c>
       <c r="R56" t="n">
-        <v>7053252</v>
+        <v>7053213</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6723,7 +6728,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6733,7 +6738,12 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6760,10 +6770,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128827181</v>
+        <v>128830607</v>
       </c>
       <c r="B57" t="n">
-        <v>57723</v>
+        <v>91538</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6771,39 +6781,34 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Getklövbäcken, Getklövbäcken, Ång</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>578677</v>
+        <v>578554</v>
       </c>
       <c r="R57" t="n">
-        <v>7053213</v>
+        <v>7053252</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6835,7 +6840,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6845,12 +6850,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>16:01</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="AD57" t="b">

--- a/artfynd/A 44372-2024 artfynd.xlsx
+++ b/artfynd/A 44372-2024 artfynd.xlsx
@@ -4703,7 +4703,7 @@
         <v>128828362</v>
       </c>
       <c r="B38" t="n">
-        <v>91721</v>
+        <v>91724</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5024,7 +5024,7 @@
         <v>128826730</v>
       </c>
       <c r="B41" t="n">
-        <v>92847</v>
+        <v>92852</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5135,7 +5135,7 @@
         <v>128827960</v>
       </c>
       <c r="B42" t="n">
-        <v>91520</v>
+        <v>91523</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5242,7 +5242,7 @@
         <v>128826236</v>
       </c>
       <c r="B43" t="n">
-        <v>91520</v>
+        <v>91523</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5349,7 +5349,7 @@
         <v>128826443</v>
       </c>
       <c r="B44" t="n">
-        <v>96770</v>
+        <v>96775</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5456,7 +5456,7 @@
         <v>128827105</v>
       </c>
       <c r="B45" t="n">
-        <v>91520</v>
+        <v>91523</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5677,45 +5677,49 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128828029</v>
+        <v>128827291</v>
       </c>
       <c r="B47" t="n">
-        <v>91805</v>
+        <v>98656</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Getklövbäcken, Getklövbäcken, Ång</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>578708</v>
+        <v>578691</v>
       </c>
       <c r="R47" t="n">
-        <v>7053135</v>
+        <v>7053218</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5747,7 +5751,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5757,7 +5761,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5784,49 +5788,45 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128827291</v>
+        <v>128828029</v>
       </c>
       <c r="B48" t="n">
-        <v>98651</v>
+        <v>91808</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Getklövbäcken, Getklövbäcken, Ång</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>578691</v>
+        <v>578708</v>
       </c>
       <c r="R48" t="n">
-        <v>7053218</v>
+        <v>7053135</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5858,7 +5858,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5868,7 +5868,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6005,7 +6005,7 @@
         <v>128828721</v>
       </c>
       <c r="B50" t="n">
-        <v>96770</v>
+        <v>96775</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6549,7 +6549,7 @@
         <v>128830025</v>
       </c>
       <c r="B55" t="n">
-        <v>91538</v>
+        <v>91541</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6653,10 +6653,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128827181</v>
+        <v>128830607</v>
       </c>
       <c r="B56" t="n">
-        <v>57723</v>
+        <v>91541</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6664,39 +6664,34 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Getklövbäcken, Getklövbäcken, Ång</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>578677</v>
+        <v>578554</v>
       </c>
       <c r="R56" t="n">
-        <v>7053213</v>
+        <v>7053252</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6728,7 +6723,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6738,12 +6733,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>16:01</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6770,10 +6760,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128830607</v>
+        <v>128827117</v>
       </c>
       <c r="B57" t="n">
-        <v>91538</v>
+        <v>79034</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6781,21 +6771,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6805,10 +6795,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>578554</v>
+        <v>578673</v>
       </c>
       <c r="R57" t="n">
-        <v>7053252</v>
+        <v>7053215</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6840,7 +6830,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6850,7 +6840,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6877,10 +6867,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128827117</v>
+        <v>128827181</v>
       </c>
       <c r="B58" t="n">
-        <v>79034</v>
+        <v>57723</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6888,34 +6878,39 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Getklövbäcken, Getklövbäcken, Ång</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>578673</v>
+        <v>578677</v>
       </c>
       <c r="R58" t="n">
-        <v>7053215</v>
+        <v>7053213</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6947,7 +6942,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6957,7 +6952,12 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7308,7 +7308,7 @@
         <v>128829015</v>
       </c>
       <c r="B62" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>

--- a/artfynd/A 44372-2024 artfynd.xlsx
+++ b/artfynd/A 44372-2024 artfynd.xlsx
@@ -4703,7 +4703,7 @@
         <v>128828362</v>
       </c>
       <c r="B38" t="n">
-        <v>91724</v>
+        <v>91727</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4810,7 +4810,7 @@
         <v>128826746</v>
       </c>
       <c r="B39" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4917,7 +4917,7 @@
         <v>128827795</v>
       </c>
       <c r="B40" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5024,7 +5024,7 @@
         <v>128826730</v>
       </c>
       <c r="B41" t="n">
-        <v>92852</v>
+        <v>92855</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5135,7 +5135,7 @@
         <v>128827960</v>
       </c>
       <c r="B42" t="n">
-        <v>91523</v>
+        <v>91526</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5242,7 +5242,7 @@
         <v>128826236</v>
       </c>
       <c r="B43" t="n">
-        <v>91523</v>
+        <v>91526</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5349,7 +5349,7 @@
         <v>128826443</v>
       </c>
       <c r="B44" t="n">
-        <v>96775</v>
+        <v>96778</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5456,7 +5456,7 @@
         <v>128827105</v>
       </c>
       <c r="B45" t="n">
-        <v>91523</v>
+        <v>91526</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5677,49 +5677,45 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128827291</v>
+        <v>128828029</v>
       </c>
       <c r="B47" t="n">
-        <v>98656</v>
+        <v>91811</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Getklövbäcken, Getklövbäcken, Ång</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>578691</v>
+        <v>578708</v>
       </c>
       <c r="R47" t="n">
-        <v>7053218</v>
+        <v>7053135</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5751,7 +5747,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5761,7 +5757,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5788,45 +5784,49 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128828029</v>
+        <v>128827291</v>
       </c>
       <c r="B48" t="n">
-        <v>91808</v>
+        <v>98659</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Getklövbäcken, Getklövbäcken, Ång</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>578708</v>
+        <v>578691</v>
       </c>
       <c r="R48" t="n">
-        <v>7053135</v>
+        <v>7053218</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5858,7 +5858,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5868,7 +5868,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5898,7 +5898,7 @@
         <v>128827406</v>
       </c>
       <c r="B49" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6005,7 +6005,7 @@
         <v>128828721</v>
       </c>
       <c r="B50" t="n">
-        <v>96775</v>
+        <v>96778</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6112,7 +6112,7 @@
         <v>128827329</v>
       </c>
       <c r="B51" t="n">
-        <v>82897</v>
+        <v>82898</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6332,10 +6332,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128826854</v>
+        <v>128827904</v>
       </c>
       <c r="B53" t="n">
-        <v>82897</v>
+        <v>79035</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6343,21 +6343,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6367,10 +6367,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>578630</v>
+        <v>578704</v>
       </c>
       <c r="R53" t="n">
-        <v>7053254</v>
+        <v>7053152</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6402,7 +6402,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6412,7 +6412,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6439,10 +6439,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128827904</v>
+        <v>128826854</v>
       </c>
       <c r="B54" t="n">
-        <v>79034</v>
+        <v>82898</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6450,21 +6450,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6474,10 +6474,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>578704</v>
+        <v>578630</v>
       </c>
       <c r="R54" t="n">
-        <v>7053152</v>
+        <v>7053254</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6509,7 +6509,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6519,7 +6519,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6549,7 +6549,7 @@
         <v>128830025</v>
       </c>
       <c r="B55" t="n">
-        <v>91541</v>
+        <v>91544</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6653,10 +6653,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128830607</v>
+        <v>128827117</v>
       </c>
       <c r="B56" t="n">
-        <v>91541</v>
+        <v>79035</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6664,21 +6664,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6688,10 +6688,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>578554</v>
+        <v>578673</v>
       </c>
       <c r="R56" t="n">
-        <v>7053252</v>
+        <v>7053215</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6723,7 +6723,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6733,7 +6733,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6760,10 +6760,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128827117</v>
+        <v>128830607</v>
       </c>
       <c r="B57" t="n">
-        <v>79034</v>
+        <v>91544</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6771,21 +6771,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6795,10 +6795,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>578673</v>
+        <v>578554</v>
       </c>
       <c r="R57" t="n">
-        <v>7053215</v>
+        <v>7053252</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6830,7 +6830,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6840,7 +6840,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6987,7 +6987,7 @@
         <v>128827078</v>
       </c>
       <c r="B59" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7094,7 +7094,7 @@
         <v>128826680</v>
       </c>
       <c r="B60" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7201,7 +7201,7 @@
         <v>128828903</v>
       </c>
       <c r="B61" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7308,7 +7308,7 @@
         <v>128829015</v>
       </c>
       <c r="B62" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>

--- a/artfynd/A 44372-2024 artfynd.xlsx
+++ b/artfynd/A 44372-2024 artfynd.xlsx
@@ -5132,32 +5132,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128827960</v>
+        <v>128826443</v>
       </c>
       <c r="B42" t="n">
-        <v>91526</v>
+        <v>96778</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1202</v>
+        <v>2869</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5167,10 +5167,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>578713</v>
+        <v>578601</v>
       </c>
       <c r="R42" t="n">
-        <v>7053139</v>
+        <v>7053281</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5202,7 +5202,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>16:39</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5212,7 +5212,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>16:39</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5239,7 +5239,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128826236</v>
+        <v>128827960</v>
       </c>
       <c r="B43" t="n">
         <v>91526</v>
@@ -5274,10 +5274,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>578567</v>
+        <v>578713</v>
       </c>
       <c r="R43" t="n">
-        <v>7053297</v>
+        <v>7053139</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5309,7 +5309,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>16:39</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5319,7 +5319,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>16:39</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5346,32 +5346,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128826443</v>
+        <v>128826236</v>
       </c>
       <c r="B44" t="n">
-        <v>96778</v>
+        <v>91526</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>2869</v>
+        <v>1202</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5381,10 +5381,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>578601</v>
+        <v>578567</v>
       </c>
       <c r="R44" t="n">
-        <v>7053281</v>
+        <v>7053297</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5416,7 +5416,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5426,7 +5426,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -6760,10 +6760,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128830607</v>
+        <v>128827181</v>
       </c>
       <c r="B57" t="n">
-        <v>91544</v>
+        <v>57723</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6771,34 +6771,39 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Getklövbäcken, Getklövbäcken, Ång</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>578554</v>
+        <v>578677</v>
       </c>
       <c r="R57" t="n">
-        <v>7053252</v>
+        <v>7053213</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6830,7 +6835,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6840,7 +6845,12 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6867,10 +6877,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128827181</v>
+        <v>128830607</v>
       </c>
       <c r="B58" t="n">
-        <v>57723</v>
+        <v>91544</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6878,39 +6888,34 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Getklövbäcken, Getklövbäcken, Ång</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>578677</v>
+        <v>578554</v>
       </c>
       <c r="R58" t="n">
-        <v>7053213</v>
+        <v>7053252</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6942,7 +6947,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6952,12 +6957,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>16:01</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="AD58" t="b">

--- a/artfynd/A 44372-2024 artfynd.xlsx
+++ b/artfynd/A 44372-2024 artfynd.xlsx
@@ -6653,10 +6653,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128827117</v>
+        <v>128830607</v>
       </c>
       <c r="B56" t="n">
-        <v>79035</v>
+        <v>91544</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6664,21 +6664,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6688,10 +6688,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>578673</v>
+        <v>578554</v>
       </c>
       <c r="R56" t="n">
-        <v>7053215</v>
+        <v>7053252</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6723,7 +6723,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6733,7 +6733,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6877,10 +6877,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128830607</v>
+        <v>128827117</v>
       </c>
       <c r="B58" t="n">
-        <v>91544</v>
+        <v>79035</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6888,21 +6888,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6912,10 +6912,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>578554</v>
+        <v>578673</v>
       </c>
       <c r="R58" t="n">
-        <v>7053252</v>
+        <v>7053215</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6947,7 +6947,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6957,7 +6957,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AD58" t="b">

--- a/artfynd/A 44372-2024 artfynd.xlsx
+++ b/artfynd/A 44372-2024 artfynd.xlsx
@@ -4703,7 +4703,7 @@
         <v>128828362</v>
       </c>
       <c r="B38" t="n">
-        <v>91727</v>
+        <v>91734</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4810,7 +4810,7 @@
         <v>128826746</v>
       </c>
       <c r="B39" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4917,7 +4917,7 @@
         <v>128827795</v>
       </c>
       <c r="B40" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5024,7 +5024,7 @@
         <v>128826730</v>
       </c>
       <c r="B41" t="n">
-        <v>92855</v>
+        <v>92862</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5135,7 +5135,7 @@
         <v>128826443</v>
       </c>
       <c r="B42" t="n">
-        <v>96778</v>
+        <v>96788</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5242,7 +5242,7 @@
         <v>128827960</v>
       </c>
       <c r="B43" t="n">
-        <v>91526</v>
+        <v>91533</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5349,7 +5349,7 @@
         <v>128826236</v>
       </c>
       <c r="B44" t="n">
-        <v>91526</v>
+        <v>91533</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5456,7 +5456,7 @@
         <v>128827105</v>
       </c>
       <c r="B45" t="n">
-        <v>91526</v>
+        <v>91533</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5563,7 +5563,7 @@
         <v>128828240</v>
       </c>
       <c r="B46" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5680,7 +5680,7 @@
         <v>128828029</v>
       </c>
       <c r="B47" t="n">
-        <v>91811</v>
+        <v>91818</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5787,7 +5787,7 @@
         <v>128827291</v>
       </c>
       <c r="B48" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5898,7 +5898,7 @@
         <v>128827406</v>
       </c>
       <c r="B49" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6005,7 +6005,7 @@
         <v>128828721</v>
       </c>
       <c r="B50" t="n">
-        <v>96778</v>
+        <v>96788</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6112,7 +6112,7 @@
         <v>128827329</v>
       </c>
       <c r="B51" t="n">
-        <v>82898</v>
+        <v>82902</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6219,7 +6219,7 @@
         <v>128826703</v>
       </c>
       <c r="B52" t="n">
-        <v>57883</v>
+        <v>57885</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6332,10 +6332,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128827904</v>
+        <v>128826854</v>
       </c>
       <c r="B53" t="n">
-        <v>79035</v>
+        <v>82902</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6343,21 +6343,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6367,10 +6367,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>578704</v>
+        <v>578630</v>
       </c>
       <c r="R53" t="n">
-        <v>7053152</v>
+        <v>7053254</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6402,7 +6402,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6412,7 +6412,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6439,10 +6439,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128826854</v>
+        <v>128827904</v>
       </c>
       <c r="B54" t="n">
-        <v>82898</v>
+        <v>79039</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6450,21 +6450,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6474,10 +6474,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>578630</v>
+        <v>578704</v>
       </c>
       <c r="R54" t="n">
-        <v>7053254</v>
+        <v>7053152</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6509,7 +6509,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6519,7 +6519,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6549,7 +6549,7 @@
         <v>128830025</v>
       </c>
       <c r="B55" t="n">
-        <v>91544</v>
+        <v>91551</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6656,7 +6656,7 @@
         <v>128830607</v>
       </c>
       <c r="B56" t="n">
-        <v>91544</v>
+        <v>91551</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6760,10 +6760,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128827181</v>
+        <v>128827117</v>
       </c>
       <c r="B57" t="n">
-        <v>57723</v>
+        <v>79039</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6771,39 +6771,34 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Getklövbäcken, Getklövbäcken, Ång</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>578677</v>
+        <v>578673</v>
       </c>
       <c r="R57" t="n">
-        <v>7053213</v>
+        <v>7053215</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6835,7 +6830,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6845,12 +6840,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>16:01</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6877,10 +6867,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128827117</v>
+        <v>128827181</v>
       </c>
       <c r="B58" t="n">
-        <v>79035</v>
+        <v>57725</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6888,34 +6878,39 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Getklövbäcken, Getklövbäcken, Ång</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>578673</v>
+        <v>578677</v>
       </c>
       <c r="R58" t="n">
-        <v>7053215</v>
+        <v>7053213</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6947,7 +6942,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6957,7 +6952,12 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6987,7 +6987,7 @@
         <v>128827078</v>
       </c>
       <c r="B59" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7094,7 +7094,7 @@
         <v>128826680</v>
       </c>
       <c r="B60" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7201,7 +7201,7 @@
         <v>128828903</v>
       </c>
       <c r="B61" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7308,7 +7308,7 @@
         <v>128829015</v>
       </c>
       <c r="B62" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>

--- a/artfynd/A 44372-2024 artfynd.xlsx
+++ b/artfynd/A 44372-2024 artfynd.xlsx
@@ -4703,7 +4703,7 @@
         <v>128828362</v>
       </c>
       <c r="B38" t="n">
-        <v>91734</v>
+        <v>91741</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5024,7 +5024,7 @@
         <v>128826730</v>
       </c>
       <c r="B41" t="n">
-        <v>92862</v>
+        <v>92869</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5135,7 +5135,7 @@
         <v>128826443</v>
       </c>
       <c r="B42" t="n">
-        <v>96788</v>
+        <v>96795</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5242,7 +5242,7 @@
         <v>128827960</v>
       </c>
       <c r="B43" t="n">
-        <v>91533</v>
+        <v>91540</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5349,7 +5349,7 @@
         <v>128826236</v>
       </c>
       <c r="B44" t="n">
-        <v>91533</v>
+        <v>91540</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5456,7 +5456,7 @@
         <v>128827105</v>
       </c>
       <c r="B45" t="n">
-        <v>91533</v>
+        <v>91540</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5680,7 +5680,7 @@
         <v>128828029</v>
       </c>
       <c r="B47" t="n">
-        <v>91818</v>
+        <v>91825</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5787,7 +5787,7 @@
         <v>128827291</v>
       </c>
       <c r="B48" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6005,7 +6005,7 @@
         <v>128828721</v>
       </c>
       <c r="B50" t="n">
-        <v>96788</v>
+        <v>96795</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6112,7 +6112,7 @@
         <v>128827329</v>
       </c>
       <c r="B51" t="n">
-        <v>82902</v>
+        <v>82871</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6335,7 +6335,7 @@
         <v>128826854</v>
       </c>
       <c r="B53" t="n">
-        <v>82902</v>
+        <v>82871</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6549,7 +6549,7 @@
         <v>128830025</v>
       </c>
       <c r="B55" t="n">
-        <v>91551</v>
+        <v>91558</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6653,10 +6653,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128830607</v>
+        <v>128827117</v>
       </c>
       <c r="B56" t="n">
-        <v>91551</v>
+        <v>79039</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6664,21 +6664,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6688,10 +6688,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>578554</v>
+        <v>578673</v>
       </c>
       <c r="R56" t="n">
-        <v>7053252</v>
+        <v>7053215</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6723,7 +6723,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6733,7 +6733,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6760,10 +6760,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128827117</v>
+        <v>128830607</v>
       </c>
       <c r="B57" t="n">
-        <v>79039</v>
+        <v>91558</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6771,21 +6771,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6795,10 +6795,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>578673</v>
+        <v>578554</v>
       </c>
       <c r="R57" t="n">
-        <v>7053215</v>
+        <v>7053252</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6830,7 +6830,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6840,7 +6840,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7308,7 +7308,7 @@
         <v>128829015</v>
       </c>
       <c r="B62" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>

--- a/artfynd/A 44372-2024 artfynd.xlsx
+++ b/artfynd/A 44372-2024 artfynd.xlsx
@@ -4703,7 +4703,7 @@
         <v>128828362</v>
       </c>
       <c r="B38" t="n">
-        <v>91741</v>
+        <v>91743</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4810,7 +4810,7 @@
         <v>128826746</v>
       </c>
       <c r="B39" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4917,7 +4917,7 @@
         <v>128827795</v>
       </c>
       <c r="B40" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5024,7 +5024,7 @@
         <v>128826730</v>
       </c>
       <c r="B41" t="n">
-        <v>92869</v>
+        <v>92871</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5132,32 +5132,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128826443</v>
+        <v>128827960</v>
       </c>
       <c r="B42" t="n">
-        <v>96795</v>
+        <v>91542</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>2869</v>
+        <v>1202</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5167,10 +5167,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>578601</v>
+        <v>578713</v>
       </c>
       <c r="R42" t="n">
-        <v>7053281</v>
+        <v>7053139</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5202,7 +5202,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>16:39</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5212,7 +5212,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>16:39</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5239,10 +5239,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128827960</v>
+        <v>128826236</v>
       </c>
       <c r="B43" t="n">
-        <v>91540</v>
+        <v>91542</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5274,10 +5274,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>578713</v>
+        <v>578567</v>
       </c>
       <c r="R43" t="n">
-        <v>7053139</v>
+        <v>7053297</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5309,7 +5309,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>16:39</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5319,7 +5319,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>16:39</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5346,32 +5346,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128826236</v>
+        <v>128826443</v>
       </c>
       <c r="B44" t="n">
-        <v>91540</v>
+        <v>96797</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1202</v>
+        <v>2869</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5381,10 +5381,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>578567</v>
+        <v>578601</v>
       </c>
       <c r="R44" t="n">
-        <v>7053297</v>
+        <v>7053281</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5416,7 +5416,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5426,7 +5426,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5456,7 +5456,7 @@
         <v>128827105</v>
       </c>
       <c r="B45" t="n">
-        <v>91540</v>
+        <v>91542</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5563,7 +5563,7 @@
         <v>128828240</v>
       </c>
       <c r="B46" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5677,45 +5677,49 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128828029</v>
+        <v>128827291</v>
       </c>
       <c r="B47" t="n">
-        <v>91825</v>
+        <v>98678</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Getklövbäcken, Getklövbäcken, Ång</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>578708</v>
+        <v>578691</v>
       </c>
       <c r="R47" t="n">
-        <v>7053135</v>
+        <v>7053218</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5747,7 +5751,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5757,7 +5761,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5784,49 +5788,45 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128827291</v>
+        <v>128828029</v>
       </c>
       <c r="B48" t="n">
-        <v>98676</v>
+        <v>91827</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Getklövbäcken, Getklövbäcken, Ång</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>578691</v>
+        <v>578708</v>
       </c>
       <c r="R48" t="n">
-        <v>7053218</v>
+        <v>7053135</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5858,7 +5858,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5868,7 +5868,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5898,7 +5898,7 @@
         <v>128827406</v>
       </c>
       <c r="B49" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6005,7 +6005,7 @@
         <v>128828721</v>
       </c>
       <c r="B50" t="n">
-        <v>96795</v>
+        <v>96797</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6112,7 +6112,7 @@
         <v>128827329</v>
       </c>
       <c r="B51" t="n">
-        <v>82871</v>
+        <v>82873</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6219,7 +6219,7 @@
         <v>128826703</v>
       </c>
       <c r="B52" t="n">
-        <v>57885</v>
+        <v>57887</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6335,7 +6335,7 @@
         <v>128826854</v>
       </c>
       <c r="B53" t="n">
-        <v>82871</v>
+        <v>82873</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6442,7 +6442,7 @@
         <v>128827904</v>
       </c>
       <c r="B54" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6549,7 +6549,7 @@
         <v>128830025</v>
       </c>
       <c r="B55" t="n">
-        <v>91558</v>
+        <v>91560</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6653,10 +6653,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128827117</v>
+        <v>128830607</v>
       </c>
       <c r="B56" t="n">
-        <v>79039</v>
+        <v>91560</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6664,21 +6664,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6688,10 +6688,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>578673</v>
+        <v>578554</v>
       </c>
       <c r="R56" t="n">
-        <v>7053215</v>
+        <v>7053252</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6723,7 +6723,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6733,7 +6733,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6760,10 +6760,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128830607</v>
+        <v>128827181</v>
       </c>
       <c r="B57" t="n">
-        <v>91558</v>
+        <v>57727</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6771,34 +6771,39 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Getklövbäcken, Getklövbäcken, Ång</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>578554</v>
+        <v>578677</v>
       </c>
       <c r="R57" t="n">
-        <v>7053252</v>
+        <v>7053213</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6830,7 +6835,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6840,7 +6845,12 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6867,10 +6877,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128827181</v>
+        <v>128827117</v>
       </c>
       <c r="B58" t="n">
-        <v>57725</v>
+        <v>79041</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6878,39 +6888,34 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Getklövbäcken, Getklövbäcken, Ång</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>578677</v>
+        <v>578673</v>
       </c>
       <c r="R58" t="n">
-        <v>7053213</v>
+        <v>7053215</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6942,7 +6947,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6952,12 +6957,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>16:01</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6987,7 +6987,7 @@
         <v>128827078</v>
       </c>
       <c r="B59" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7094,7 +7094,7 @@
         <v>128826680</v>
       </c>
       <c r="B60" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7201,7 +7201,7 @@
         <v>128828903</v>
       </c>
       <c r="B61" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7308,7 +7308,7 @@
         <v>128829015</v>
       </c>
       <c r="B62" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>

--- a/artfynd/A 44372-2024 artfynd.xlsx
+++ b/artfynd/A 44372-2024 artfynd.xlsx
@@ -6653,10 +6653,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128830607</v>
+        <v>128827181</v>
       </c>
       <c r="B56" t="n">
-        <v>91560</v>
+        <v>57727</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6664,34 +6664,39 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Getklövbäcken, Getklövbäcken, Ång</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>578554</v>
+        <v>578677</v>
       </c>
       <c r="R56" t="n">
-        <v>7053252</v>
+        <v>7053213</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6723,7 +6728,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6733,7 +6738,12 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6760,10 +6770,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128827181</v>
+        <v>128830607</v>
       </c>
       <c r="B57" t="n">
-        <v>57727</v>
+        <v>91560</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6771,39 +6781,34 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Getklövbäcken, Getklövbäcken, Ång</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>578677</v>
+        <v>578554</v>
       </c>
       <c r="R57" t="n">
-        <v>7053213</v>
+        <v>7053252</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6835,7 +6840,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6845,12 +6850,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>16:01</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="AD57" t="b">

--- a/artfynd/A 44372-2024 artfynd.xlsx
+++ b/artfynd/A 44372-2024 artfynd.xlsx
@@ -5132,32 +5132,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128827960</v>
+        <v>128826443</v>
       </c>
       <c r="B42" t="n">
-        <v>91542</v>
+        <v>96797</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1202</v>
+        <v>2869</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5167,10 +5167,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>578713</v>
+        <v>578601</v>
       </c>
       <c r="R42" t="n">
-        <v>7053139</v>
+        <v>7053281</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5202,7 +5202,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>16:39</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5212,7 +5212,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>16:39</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5239,7 +5239,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128826236</v>
+        <v>128827960</v>
       </c>
       <c r="B43" t="n">
         <v>91542</v>
@@ -5274,10 +5274,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>578567</v>
+        <v>578713</v>
       </c>
       <c r="R43" t="n">
-        <v>7053297</v>
+        <v>7053139</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5309,7 +5309,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>16:39</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5319,7 +5319,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>16:39</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5346,32 +5346,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128826443</v>
+        <v>128826236</v>
       </c>
       <c r="B44" t="n">
-        <v>96797</v>
+        <v>91542</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>2869</v>
+        <v>1202</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5381,10 +5381,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>578601</v>
+        <v>578567</v>
       </c>
       <c r="R44" t="n">
-        <v>7053281</v>
+        <v>7053297</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5416,7 +5416,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5426,7 +5426,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -6653,10 +6653,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128827181</v>
+        <v>128827117</v>
       </c>
       <c r="B56" t="n">
-        <v>57727</v>
+        <v>79041</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6664,39 +6664,34 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Getklövbäcken, Getklövbäcken, Ång</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>578677</v>
+        <v>578673</v>
       </c>
       <c r="R56" t="n">
-        <v>7053213</v>
+        <v>7053215</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6728,7 +6723,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6738,12 +6733,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>16:01</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6770,10 +6760,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128830607</v>
+        <v>128827181</v>
       </c>
       <c r="B57" t="n">
-        <v>91560</v>
+        <v>57727</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6781,34 +6771,39 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Getklövbäcken, Getklövbäcken, Ång</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>578554</v>
+        <v>578677</v>
       </c>
       <c r="R57" t="n">
-        <v>7053252</v>
+        <v>7053213</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6840,7 +6835,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6850,7 +6845,12 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6877,10 +6877,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128827117</v>
+        <v>128830607</v>
       </c>
       <c r="B58" t="n">
-        <v>79041</v>
+        <v>91560</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6888,21 +6888,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6912,10 +6912,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>578673</v>
+        <v>578554</v>
       </c>
       <c r="R58" t="n">
-        <v>7053215</v>
+        <v>7053252</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6947,7 +6947,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6957,7 +6957,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="AD58" t="b">

--- a/artfynd/A 44372-2024 artfynd.xlsx
+++ b/artfynd/A 44372-2024 artfynd.xlsx
@@ -4703,7 +4703,7 @@
         <v>128828362</v>
       </c>
       <c r="B38" t="n">
-        <v>91743</v>
+        <v>91752</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5024,7 +5024,7 @@
         <v>128826730</v>
       </c>
       <c r="B41" t="n">
-        <v>92871</v>
+        <v>92857</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5135,7 +5135,7 @@
         <v>128826443</v>
       </c>
       <c r="B42" t="n">
-        <v>96797</v>
+        <v>96823</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5242,7 +5242,7 @@
         <v>128827960</v>
       </c>
       <c r="B43" t="n">
-        <v>91542</v>
+        <v>91540</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5349,7 +5349,7 @@
         <v>128826236</v>
       </c>
       <c r="B44" t="n">
-        <v>91542</v>
+        <v>91540</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5456,7 +5456,7 @@
         <v>128827105</v>
       </c>
       <c r="B45" t="n">
-        <v>91542</v>
+        <v>91540</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5680,7 +5680,7 @@
         <v>128827291</v>
       </c>
       <c r="B47" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5791,7 +5791,7 @@
         <v>128828029</v>
       </c>
       <c r="B48" t="n">
-        <v>91827</v>
+        <v>91837</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6005,7 +6005,7 @@
         <v>128828721</v>
       </c>
       <c r="B50" t="n">
-        <v>96797</v>
+        <v>96823</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6549,7 +6549,7 @@
         <v>128830025</v>
       </c>
       <c r="B55" t="n">
-        <v>91560</v>
+        <v>91558</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6653,10 +6653,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128827117</v>
+        <v>128830607</v>
       </c>
       <c r="B56" t="n">
-        <v>79041</v>
+        <v>91558</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6664,21 +6664,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6688,10 +6688,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>578673</v>
+        <v>578554</v>
       </c>
       <c r="R56" t="n">
-        <v>7053215</v>
+        <v>7053252</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6723,7 +6723,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6733,7 +6733,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6760,10 +6760,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128827181</v>
+        <v>128827117</v>
       </c>
       <c r="B57" t="n">
-        <v>57727</v>
+        <v>79041</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6771,39 +6771,34 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Getklövbäcken, Getklövbäcken, Ång</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>578677</v>
+        <v>578673</v>
       </c>
       <c r="R57" t="n">
-        <v>7053213</v>
+        <v>7053215</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6835,7 +6830,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6845,12 +6840,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>16:01</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6877,10 +6867,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128830607</v>
+        <v>128827181</v>
       </c>
       <c r="B58" t="n">
-        <v>91560</v>
+        <v>57727</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6888,34 +6878,39 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Getklövbäcken, Getklövbäcken, Ång</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>578554</v>
+        <v>578677</v>
       </c>
       <c r="R58" t="n">
-        <v>7053252</v>
+        <v>7053213</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6947,7 +6942,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6957,7 +6952,12 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7308,7 +7308,7 @@
         <v>128829015</v>
       </c>
       <c r="B62" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>

--- a/artfynd/A 44372-2024 artfynd.xlsx
+++ b/artfynd/A 44372-2024 artfynd.xlsx
@@ -4703,7 +4703,7 @@
         <v>128828362</v>
       </c>
       <c r="B38" t="n">
-        <v>91752</v>
+        <v>91753</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5024,7 +5024,7 @@
         <v>128826730</v>
       </c>
       <c r="B41" t="n">
-        <v>92857</v>
+        <v>92858</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5132,32 +5132,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128826443</v>
+        <v>128827960</v>
       </c>
       <c r="B42" t="n">
-        <v>96823</v>
+        <v>91540</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>2869</v>
+        <v>1202</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5167,10 +5167,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>578601</v>
+        <v>578713</v>
       </c>
       <c r="R42" t="n">
-        <v>7053281</v>
+        <v>7053139</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5202,7 +5202,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>16:39</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5212,7 +5212,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>16:39</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5239,32 +5239,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128827960</v>
+        <v>128826443</v>
       </c>
       <c r="B43" t="n">
-        <v>91540</v>
+        <v>96824</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1202</v>
+        <v>2869</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5274,10 +5274,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>578713</v>
+        <v>578601</v>
       </c>
       <c r="R43" t="n">
-        <v>7053139</v>
+        <v>7053281</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5309,7 +5309,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>16:39</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5319,7 +5319,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>16:39</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5677,49 +5677,45 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128827291</v>
+        <v>128828029</v>
       </c>
       <c r="B47" t="n">
-        <v>98704</v>
+        <v>91838</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Getklövbäcken, Getklövbäcken, Ång</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>578691</v>
+        <v>578708</v>
       </c>
       <c r="R47" t="n">
-        <v>7053218</v>
+        <v>7053135</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5751,7 +5747,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5761,7 +5757,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5788,45 +5784,49 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128828029</v>
+        <v>128827291</v>
       </c>
       <c r="B48" t="n">
-        <v>91837</v>
+        <v>98705</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Getklövbäcken, Getklövbäcken, Ång</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>578708</v>
+        <v>578691</v>
       </c>
       <c r="R48" t="n">
-        <v>7053135</v>
+        <v>7053218</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5858,7 +5858,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5868,7 +5868,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6005,7 +6005,7 @@
         <v>128828721</v>
       </c>
       <c r="B50" t="n">
-        <v>96823</v>
+        <v>96824</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6332,10 +6332,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128826854</v>
+        <v>128827904</v>
       </c>
       <c r="B53" t="n">
-        <v>82873</v>
+        <v>79041</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6343,21 +6343,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6367,10 +6367,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>578630</v>
+        <v>578704</v>
       </c>
       <c r="R53" t="n">
-        <v>7053254</v>
+        <v>7053152</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6402,7 +6402,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6412,7 +6412,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6439,10 +6439,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128827904</v>
+        <v>128826854</v>
       </c>
       <c r="B54" t="n">
-        <v>79041</v>
+        <v>82873</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6450,21 +6450,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6474,10 +6474,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>578704</v>
+        <v>578630</v>
       </c>
       <c r="R54" t="n">
-        <v>7053152</v>
+        <v>7053254</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6509,7 +6509,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6519,7 +6519,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6549,7 +6549,7 @@
         <v>128830025</v>
       </c>
       <c r="B55" t="n">
-        <v>91558</v>
+        <v>91560</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6566,14 +6566,10 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
-        </is>
-      </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr"/>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
@@ -6656,7 +6652,7 @@
         <v>128830607</v>
       </c>
       <c r="B56" t="n">
-        <v>91558</v>
+        <v>91560</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6673,14 +6669,10 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
-        </is>
-      </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr"/>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
@@ -7308,7 +7300,7 @@
         <v>128829015</v>
       </c>
       <c r="B62" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>

--- a/artfynd/A 44372-2024 artfynd.xlsx
+++ b/artfynd/A 44372-2024 artfynd.xlsx
@@ -4807,7 +4807,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128826746</v>
+        <v>128827795</v>
       </c>
       <c r="B39" t="n">
         <v>79041</v>
@@ -4842,10 +4842,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>578626</v>
+        <v>578718</v>
       </c>
       <c r="R39" t="n">
-        <v>7053261</v>
+        <v>7053164</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4877,7 +4877,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4887,7 +4887,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4914,7 +4914,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128827795</v>
+        <v>128826746</v>
       </c>
       <c r="B40" t="n">
         <v>79041</v>
@@ -4949,10 +4949,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>578718</v>
+        <v>578626</v>
       </c>
       <c r="R40" t="n">
-        <v>7053164</v>
+        <v>7053261</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4984,7 +4984,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4994,7 +4994,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5239,32 +5239,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128826443</v>
+        <v>128826236</v>
       </c>
       <c r="B43" t="n">
-        <v>96824</v>
+        <v>91540</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>2869</v>
+        <v>1202</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5274,10 +5274,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>578601</v>
+        <v>578567</v>
       </c>
       <c r="R43" t="n">
-        <v>7053281</v>
+        <v>7053297</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5309,7 +5309,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5319,7 +5319,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5346,32 +5346,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128826236</v>
+        <v>128826443</v>
       </c>
       <c r="B44" t="n">
-        <v>91540</v>
+        <v>96825</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1202</v>
+        <v>2869</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5381,10 +5381,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>578567</v>
+        <v>578601</v>
       </c>
       <c r="R44" t="n">
-        <v>7053297</v>
+        <v>7053281</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5416,7 +5416,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5426,7 +5426,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5787,7 +5787,7 @@
         <v>128827291</v>
       </c>
       <c r="B48" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6005,7 +6005,7 @@
         <v>128828721</v>
       </c>
       <c r="B50" t="n">
-        <v>96824</v>
+        <v>96825</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6332,10 +6332,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128827904</v>
+        <v>128826854</v>
       </c>
       <c r="B53" t="n">
-        <v>79041</v>
+        <v>82873</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6343,21 +6343,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6367,10 +6367,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>578704</v>
+        <v>578630</v>
       </c>
       <c r="R53" t="n">
-        <v>7053152</v>
+        <v>7053254</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6402,7 +6402,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6412,7 +6412,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6439,10 +6439,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128826854</v>
+        <v>128827904</v>
       </c>
       <c r="B54" t="n">
-        <v>82873</v>
+        <v>79041</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6450,21 +6450,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6474,10 +6474,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>578630</v>
+        <v>578704</v>
       </c>
       <c r="R54" t="n">
-        <v>7053254</v>
+        <v>7053152</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6509,7 +6509,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6519,7 +6519,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -7300,7 +7300,7 @@
         <v>128829015</v>
       </c>
       <c r="B62" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
